--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -1097,10 +1097,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>86.7</x:v>
+        <x:v>82.1</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-3.3</x:v>
+        <x:v>-4.6</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1126,10 +1126,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>17</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
@@ -1155,10 +1155,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>12.19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>16</x:v>
@@ -1184,10 +1184,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>37.88</x:v>
+        <x:v>37.1</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.66</x:v>
+        <x:v>-0.78</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>18</x:v>
@@ -1213,10 +1213,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>20</x:v>
@@ -1242,10 +1242,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>73.4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>1.75</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>20</x:v>
@@ -1271,10 +1271,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>24</x:v>
@@ -1300,10 +1300,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>26</x:v>
@@ -1329,10 +1329,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>26</x:v>
@@ -1358,10 +1358,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>66.1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-0.4</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>26</x:v>
@@ -1387,10 +1387,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>26</x:v>
@@ -1416,10 +1416,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>30.98</x:v>
+        <x:v>30.78</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>26</x:v>
@@ -1445,10 +1445,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>32</x:v>
@@ -1474,10 +1474,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>33</x:v>
@@ -1503,10 +1503,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>33</x:v>
@@ -1532,10 +1532,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>169</x:v>
+        <x:v>164.9</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-4.7</x:v>
+        <x:v>-4.1</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>36</x:v>
@@ -1561,10 +1561,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>37</x:v>
@@ -1590,10 +1590,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>37</x:v>
@@ -1619,10 +1619,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>37</x:v>
@@ -1648,10 +1648,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>36.1</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>41</x:v>
@@ -1677,10 +1677,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>79.3</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>2.2</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>41</x:v>
@@ -1706,10 +1706,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>43</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>114.6</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>-1.6</x:v>
@@ -1764,10 +1764,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>701</x:v>
+        <x:v>682.5</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-18.5</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>46</x:v>
@@ -1793,10 +1793,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>48</x:v>
@@ -1822,10 +1822,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>48</x:v>
@@ -1851,10 +1851,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>50</x:v>
@@ -1880,10 +1880,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>50</x:v>
@@ -1909,10 +1909,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>32.06</x:v>
+        <x:v>31.04</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-1.02</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>52</x:v>
@@ -1938,10 +1938,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>18.08</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.78</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>52</x:v>
@@ -1967,10 +1967,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>79.3</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>2.2</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>52</x:v>
@@ -1996,10 +1996,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>54</x:v>
@@ -2025,10 +2025,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>169</x:v>
+        <x:v>164.9</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-4.7</x:v>
+        <x:v>-4.1</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>54</x:v>
@@ -2054,10 +2054,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>701</x:v>
+        <x:v>682.5</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-18.5</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>55</x:v>
@@ -2083,10 +2083,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>55</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>55</x:v>
@@ -2141,10 +2141,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>55</x:v>
@@ -2170,10 +2170,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>58</x:v>
@@ -2199,10 +2199,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>17</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>59</x:v>
@@ -2228,10 +2228,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>12.69</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>61</x:v>
@@ -2257,10 +2257,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>61</x:v>
@@ -2286,10 +2286,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>62</x:v>
@@ -2315,10 +2315,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>62</x:v>
@@ -2344,10 +2344,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>24.72</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>1.1</x:v>
+        <x:v>-2.46</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>64</x:v>
@@ -2373,10 +2373,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>65</x:v>
@@ -2402,10 +2402,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>65</x:v>
@@ -2431,10 +2431,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>65</x:v>
@@ -2460,10 +2460,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>67</x:v>
@@ -2489,10 +2489,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>67</x:v>
@@ -2518,10 +2518,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>68</x:v>
@@ -2547,10 +2547,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>68</x:v>
@@ -2576,10 +2576,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>3.93</x:v>
+        <x:v>3.81</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>70</x:v>
@@ -2605,10 +2605,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>72</x:v>
@@ -2634,10 +2634,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>72</x:v>
@@ -2663,10 +2663,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>72</x:v>
@@ -2692,10 +2692,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>72</x:v>
@@ -2721,10 +2721,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>73</x:v>
@@ -2750,10 +2750,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>79.3</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>2.2</x:v>
+        <x:v>7.9</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>73</x:v>
@@ -2779,10 +2779,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>74</x:v>
@@ -2808,10 +2808,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>31.64</x:v>
+        <x:v>30.72</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>74</x:v>
@@ -2837,10 +2837,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>12.37</x:v>
+        <x:v>12.47</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>74</x:v>
@@ -2866,10 +2866,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>77</x:v>
@@ -2895,10 +2895,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>17</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>78</x:v>
@@ -2924,10 +2924,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>12.37</x:v>
+        <x:v>12.47</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>78</x:v>
@@ -2953,10 +2953,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>78</x:v>
@@ -2982,10 +2982,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>81</x:v>
@@ -3011,10 +3011,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>78.9</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>81</x:v>
@@ -3040,10 +3040,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>81</x:v>
@@ -3069,10 +3069,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>84</x:v>
@@ -3098,10 +3098,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>84</x:v>
@@ -3127,10 +3127,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>85</x:v>
@@ -3156,10 +3156,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>85</x:v>
@@ -3185,10 +3185,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>18.08</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.78</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>85</x:v>
@@ -3214,10 +3214,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>86</x:v>
@@ -3243,10 +3243,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>86</x:v>
@@ -3272,10 +3272,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>86</x:v>
@@ -3301,10 +3301,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>86</x:v>
@@ -3330,10 +3330,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>86</x:v>
@@ -3359,10 +3359,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>89</x:v>
@@ -3388,10 +3388,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>89</x:v>
@@ -3417,10 +3417,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>89</x:v>
@@ -3446,10 +3446,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>90</x:v>
@@ -3475,10 +3475,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>90</x:v>
@@ -3504,10 +3504,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>60.85</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>90</x:v>
@@ -3533,10 +3533,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>92</x:v>
@@ -3562,10 +3562,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>92</x:v>
@@ -3591,10 +3591,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>92</x:v>
@@ -3620,10 +3620,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>92</x:v>
@@ -3649,10 +3649,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>92</x:v>
@@ -3678,10 +3678,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>93</x:v>
@@ -3707,10 +3707,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>93</x:v>
@@ -3736,10 +3736,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>8.12</x:v>
+        <x:v>7.98</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>96</x:v>
@@ -3765,10 +3765,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>96</x:v>
@@ -3794,10 +3794,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>98</x:v>
@@ -3823,10 +3823,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>99</x:v>
@@ -3852,10 +3852,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>99</x:v>
@@ -3881,10 +3881,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>99</x:v>
@@ -3910,10 +3910,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -3939,10 +3939,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>101</x:v>
@@ -3968,10 +3968,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>102</x:v>
@@ -3997,10 +3997,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>46.88</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.28</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>102</x:v>
@@ -4026,10 +4026,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>104</x:v>
@@ -4055,10 +4055,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>104</x:v>
@@ -4084,10 +4084,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>105</x:v>
@@ -4113,10 +4113,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>24.72</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>1.1</x:v>
+        <x:v>-2.46</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>106</x:v>
@@ -4142,10 +4142,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>17.9</x:v>
+        <x:v>17.87</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>106</x:v>
@@ -4171,10 +4171,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>12.19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>108</x:v>
@@ -4200,10 +4200,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>108</x:v>
@@ -4229,10 +4229,10 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>36.2</x:v>
+        <x:v>35.86</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-2.42</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>108</x:v>
@@ -4258,10 +4258,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>111</x:v>
@@ -4287,10 +4287,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>12.19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>111</x:v>
@@ -4316,10 +4316,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>112</x:v>
@@ -4345,10 +4345,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>73.4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>1.75</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>112</x:v>
@@ -4374,10 +4374,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>36.1</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>113</x:v>
@@ -4403,10 +4403,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>113</x:v>
@@ -4432,10 +4432,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>80.6</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>115</x:v>
@@ -4461,10 +4461,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>116</x:v>
@@ -4490,10 +4490,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>116</x:v>
@@ -4519,10 +4519,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>116</x:v>
@@ -4548,10 +4548,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>116</x:v>
@@ -4577,10 +4577,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>117</x:v>
@@ -4606,10 +4606,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.26</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>-3.06</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>119</x:v>
@@ -4635,10 +4635,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>120</x:v>
@@ -4664,10 +4664,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>121</x:v>
@@ -4693,10 +4693,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>121</x:v>
@@ -4722,10 +4722,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>122</x:v>
@@ -4751,10 +4751,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>123</x:v>
@@ -4780,10 +4780,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>701</x:v>
+        <x:v>682.5</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-18.5</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>123</x:v>
@@ -4809,10 +4809,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>123</x:v>
@@ -4838,10 +4838,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>123</x:v>
@@ -4867,10 +4867,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>73.4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>1.75</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>124</x:v>
@@ -4896,10 +4896,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>125</x:v>
@@ -4925,10 +4925,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>125</x:v>
@@ -4954,10 +4954,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>125</x:v>
@@ -4983,10 +4983,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>126</x:v>
@@ -5012,10 +5012,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>127</x:v>
@@ -5041,10 +5041,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>127</x:v>
@@ -5070,10 +5070,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>129</x:v>
@@ -5099,10 +5099,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>130</x:v>
@@ -5128,10 +5128,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>130</x:v>
@@ -5157,10 +5157,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>131</x:v>
@@ -5186,10 +5186,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>132</x:v>
@@ -5215,10 +5215,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>132</x:v>
@@ -5244,10 +5244,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>133</x:v>
@@ -5273,10 +5273,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>133</x:v>
@@ -5302,10 +5302,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>134</x:v>
@@ -5331,10 +5331,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.26</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>-3.06</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>134</x:v>
@@ -5360,10 +5360,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>30.48</x:v>
+        <x:v>29.44</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>-0.96</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>134</x:v>
@@ -5389,10 +5389,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>36.1</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>136</x:v>
@@ -5418,10 +5418,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>136</x:v>
@@ -5447,10 +5447,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>136</x:v>
@@ -5476,10 +5476,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>4.8</x:v>
+        <x:v>4.64</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>136</x:v>
@@ -5505,10 +5505,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>136</x:v>
@@ -5534,10 +5534,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.26</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>-3.06</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>136</x:v>
@@ -5563,10 +5563,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>138</x:v>
@@ -5592,10 +5592,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>36.1</x:v>
+        <x:v>33.88</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>138</x:v>
@@ -5621,10 +5621,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>138</x:v>
@@ -5650,10 +5650,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>139</x:v>
@@ -5679,10 +5679,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>140</x:v>
@@ -5708,10 +5708,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>140</x:v>
@@ -5737,10 +5737,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>140</x:v>
@@ -5766,10 +5766,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>141</x:v>
@@ -5795,10 +5795,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>141</x:v>
@@ -5824,10 +5824,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.26</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>-3.06</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>141</x:v>
@@ -5853,10 +5853,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>142</x:v>
@@ -5882,10 +5882,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>142</x:v>
@@ -5911,10 +5911,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>143</x:v>
@@ -5940,10 +5940,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>143</x:v>
@@ -5969,10 +5969,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>143</x:v>
@@ -5998,10 +5998,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>701</x:v>
+        <x:v>682.5</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-18.5</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>144</x:v>
@@ -6027,10 +6027,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>144</x:v>
@@ -6056,10 +6056,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>144</x:v>
@@ -6085,10 +6085,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>144</x:v>
@@ -6114,10 +6114,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>145</x:v>
@@ -6143,10 +6143,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>145</x:v>
@@ -6172,10 +6172,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>145</x:v>
@@ -6201,10 +6201,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>145</x:v>
@@ -6230,10 +6230,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>80.6</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>146</x:v>
@@ -6259,10 +6259,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>64.15</x:v>
+        <x:v>62.15</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>-3.65</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>146</x:v>
@@ -6288,10 +6288,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>148</x:v>
@@ -6317,10 +6317,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>38.94</x:v>
+        <x:v>37.84</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-1.1</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>150</x:v>
@@ -6346,10 +6346,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>151</x:v>
@@ -6375,10 +6375,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>151</x:v>
@@ -6404,10 +6404,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>151</x:v>
@@ -6433,10 +6433,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>169.7</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>-3.9</x:v>
+        <x:v>-6.7</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>151</x:v>
@@ -6462,10 +6462,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>4.06</x:v>
+        <x:v>3.94</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>151</x:v>
@@ -6491,10 +6491,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>4.06</x:v>
+        <x:v>3.94</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>151</x:v>
@@ -6520,10 +6520,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>153</x:v>
@@ -6549,10 +6549,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>153</x:v>
@@ -6578,10 +6578,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>153</x:v>
@@ -6607,10 +6607,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>12.45</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>155</x:v>
@@ -6636,10 +6636,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>12.45</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>155</x:v>
@@ -6665,10 +6665,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>12.45</x:v>
+        <x:v>11.89</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.56</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>155</x:v>
@@ -6694,10 +6694,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>155</x:v>
@@ -6723,10 +6723,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>157</x:v>
@@ -6752,10 +6752,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>157</x:v>
@@ -6781,10 +6781,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>158</x:v>
@@ -6810,10 +6810,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B199" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>159</x:v>
@@ -6839,10 +6839,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>159</x:v>
@@ -6868,10 +6868,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>28.92</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>2.62</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>159</x:v>
@@ -6897,10 +6897,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>4.8</x:v>
+        <x:v>4.64</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>159</x:v>
@@ -6926,10 +6926,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>4.8</x:v>
+        <x:v>4.64</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>159</x:v>
@@ -6955,10 +6955,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>275</x:v>
+        <x:v>292.5</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>25</x:v>
+        <x:v>17.5</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>162</x:v>
@@ -6984,10 +6984,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>162</x:v>
@@ -7013,10 +7013,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>163</x:v>
@@ -7042,10 +7042,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>163</x:v>
@@ -7071,10 +7071,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B208" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>163</x:v>
@@ -7100,10 +7100,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>28.92</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>2.62</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>164</x:v>
@@ -7129,10 +7129,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>28.92</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>2.62</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>164</x:v>
@@ -7158,10 +7158,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>40.98</x:v>
+        <x:v>39.6</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-1.38</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>164</x:v>
@@ -7187,10 +7187,10 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>22.26</x:v>
+        <x:v>21.66</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>0.38</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>164</x:v>
@@ -7216,10 +7216,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>80.6</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>167</x:v>
@@ -7245,10 +7245,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>167</x:v>
@@ -7274,10 +7274,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>168</x:v>
@@ -7303,10 +7303,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>94.9</x:v>
+        <x:v>98.35</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>-2.15</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>170</x:v>
@@ -7332,10 +7332,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>170</x:v>
@@ -7361,10 +7361,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>171</x:v>
@@ -7390,10 +7390,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>171</x:v>
@@ -7419,10 +7419,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>171</x:v>
@@ -7448,10 +7448,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>171</x:v>
@@ -7477,10 +7477,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>28.92</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>2.62</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>171</x:v>
@@ -7506,10 +7506,10 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B223" s="0">
-        <x:v>20.2</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>171</x:v>
@@ -7535,10 +7535,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>171</x:v>
@@ -7564,10 +7564,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>171</x:v>
@@ -7593,10 +7593,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>173</x:v>
@@ -7622,10 +7622,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>173</x:v>
@@ -7651,10 +7651,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>173</x:v>
@@ -7680,10 +7680,10 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B229" s="0">
-        <x:v>64.15</x:v>
+        <x:v>62.15</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>-3.65</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>173</x:v>
@@ -7709,10 +7709,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>174</x:v>
@@ -7738,10 +7738,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>174</x:v>
@@ -7767,10 +7767,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>174</x:v>
@@ -7796,10 +7796,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>9.39</x:v>
+        <x:v>9.06</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>176</x:v>
@@ -7825,10 +7825,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>177</x:v>
@@ -7854,10 +7854,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>177</x:v>
@@ -7883,10 +7883,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.26</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>-1.2</x:v>
+        <x:v>-3.06</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>177</x:v>
@@ -7912,10 +7912,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>178</x:v>
@@ -7941,10 +7941,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B238" s="0">
-        <x:v>17</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>178</x:v>
@@ -7970,10 +7970,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>179</x:v>
@@ -7999,10 +7999,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>180</x:v>
@@ -8028,10 +8028,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>180</x:v>
@@ -8057,10 +8057,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>180</x:v>
@@ -8086,10 +8086,10 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>20.2</x:v>
+        <x:v>20.08</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>181</x:v>
@@ -8115,10 +8115,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>182</x:v>
@@ -8144,10 +8144,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>18.08</x:v>
+        <x:v>17.3</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.78</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>183</x:v>
@@ -8173,10 +8173,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>184</x:v>
@@ -8202,10 +8202,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>184</x:v>
@@ -8231,10 +8231,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>185</x:v>
@@ -8260,10 +8260,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>186</x:v>
@@ -8289,10 +8289,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>186</x:v>
@@ -8318,10 +8318,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>30.48</x:v>
+        <x:v>29.44</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>-0.96</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>187</x:v>
@@ -8347,10 +8347,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B252" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>187</x:v>
@@ -8376,10 +8376,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>60.85</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>188</x:v>
@@ -8405,10 +8405,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>4.58</x:v>
+        <x:v>4.43</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>189</x:v>
@@ -8434,10 +8434,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>189</x:v>
@@ -8463,10 +8463,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>189</x:v>
@@ -8492,10 +8492,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>189</x:v>
@@ -8521,10 +8521,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>190</x:v>
@@ -8550,10 +8550,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>15.08</x:v>
+        <x:v>14.18</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>190</x:v>
@@ -8579,10 +8579,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>190</x:v>
@@ -8608,10 +8608,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>192</x:v>
@@ -8637,10 +8637,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>193</x:v>
@@ -8666,10 +8666,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>194</x:v>
@@ -8695,10 +8695,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>73.4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>1.75</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>194</x:v>
@@ -8724,10 +8724,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>194</x:v>
@@ -8753,10 +8753,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>195</x:v>
@@ -8782,10 +8782,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>195</x:v>
@@ -8811,10 +8811,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>46.88</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.28</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>195</x:v>
@@ -8840,10 +8840,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>195</x:v>
@@ -8869,10 +8869,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>197</x:v>
@@ -8898,10 +8898,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B271" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>198</x:v>
@@ -8927,10 +8927,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B272" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>198</x:v>
@@ -8956,10 +8956,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>199</x:v>
@@ -8985,10 +8985,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>61.7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>-2.05</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>200</x:v>
@@ -9014,10 +9014,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>200</x:v>
@@ -9043,10 +9043,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>200</x:v>
@@ -9072,10 +9072,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>3.5</x:v>
+        <x:v>3.48</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>202</x:v>
@@ -9101,10 +9101,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>32.06</x:v>
+        <x:v>31.04</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-1.02</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>202</x:v>
@@ -9130,10 +9130,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>20.7</x:v>
+        <x:v>19.95</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>203</x:v>
@@ -9159,10 +9159,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>204</x:v>
@@ -9188,10 +9188,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>46.88</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.28</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>205</x:v>
@@ -9217,10 +9217,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>205</x:v>
@@ -9246,10 +9246,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>31.64</x:v>
+        <x:v>30.72</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-0.48</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>206</x:v>
@@ -9275,10 +9275,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B284" s="0">
-        <x:v>34.44</x:v>
+        <x:v>34.34</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>3.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>206</x:v>
@@ -9304,10 +9304,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>207</x:v>
@@ -9333,10 +9333,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>207</x:v>
@@ -9362,10 +9362,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B287" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>207</x:v>
@@ -9391,10 +9391,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>207</x:v>
@@ -9420,10 +9420,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>207</x:v>
@@ -9449,10 +9449,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>207</x:v>
@@ -9478,10 +9478,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>208</x:v>
@@ -9507,10 +9507,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>21.92</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.92</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>209</x:v>
@@ -9536,10 +9536,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>209</x:v>
@@ -9565,10 +9565,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>30.22</x:v>
+        <x:v>29.46</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>210</x:v>
@@ -9594,10 +9594,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>28.92</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>2.62</x:v>
+        <x:v>0.86</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>210</x:v>
@@ -9623,10 +9623,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>38.94</x:v>
+        <x:v>37.84</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-1.1</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>210</x:v>
@@ -9652,10 +9652,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>393.75</x:v>
+        <x:v>372.5</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>-4.75</x:v>
+        <x:v>-21.25</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>211</x:v>
@@ -9681,10 +9681,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B298" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>211</x:v>
@@ -9710,10 +9710,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>12.19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>211</x:v>
@@ -9739,10 +9739,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>211</x:v>
@@ -9768,10 +9768,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>32.06</x:v>
+        <x:v>31.04</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-1.02</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>211</x:v>
@@ -9797,10 +9797,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B302" s="0">
-        <x:v>43.54</x:v>
+        <x:v>44.5</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>0.48</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>213</x:v>
@@ -9826,10 +9826,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>60.85</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>213</x:v>
@@ -9855,10 +9855,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>60.85</x:v>
+        <x:v>14.49</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>-1.15</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>213</x:v>
@@ -9884,10 +9884,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>46.88</x:v>
+        <x:v>43.6</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-3.28</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>213</x:v>
@@ -9913,10 +9913,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B306" s="0">
-        <x:v>14.26</x:v>
+        <x:v>13.62</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>0.01</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>213</x:v>
@@ -9942,10 +9942,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>5.31</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>215</x:v>
@@ -9971,10 +9971,10 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>20.22</x:v>
+        <x:v>19.81</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.41</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>215</x:v>
@@ -10000,10 +10000,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>215</x:v>
@@ -10029,10 +10029,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>80.6</x:v>
+        <x:v>81.65</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>1.05</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>217</x:v>
@@ -10058,10 +10058,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>38.94</x:v>
+        <x:v>37.84</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-1.1</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>217</x:v>
@@ -10087,10 +10087,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>4650</x:v>
+        <x:v>4830</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>200</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>217</x:v>
@@ -10116,10 +10116,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>218</x:v>
@@ -10145,10 +10145,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>43.54</x:v>
+        <x:v>44.5</x:v>
       </x:c>
       <x:c r="C314" s="0">
-        <x:v>0.48</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
         <x:v>218</x:v>
@@ -10174,10 +10174,10 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>5.83</x:v>
+        <x:v>5.9</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>218</x:v>
@@ -10203,10 +10203,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>218</x:v>
@@ -10232,10 +10232,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.1</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.3</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>218</x:v>
@@ -10261,10 +10261,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>218</x:v>
@@ -10290,10 +10290,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>32.34</x:v>
+        <x:v>31.4</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.94</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>221</x:v>
@@ -10319,10 +10319,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>43.54</x:v>
+        <x:v>44.5</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>0.48</x:v>
+        <x:v>0.96</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>222</x:v>
@@ -10348,10 +10348,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>17.41</x:v>
+        <x:v>16.82</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>223</x:v>
@@ -10377,10 +10377,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>223</x:v>
@@ -10406,10 +10406,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>17.49</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.87</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>224</x:v>
@@ -10435,10 +10435,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>23</x:v>
+        <x:v>22.74</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>225</x:v>
@@ -10464,10 +10464,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>3.88</x:v>
+        <x:v>3.82</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>227</x:v>
@@ -10493,10 +10493,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>128.8</x:v>
+        <x:v>119.6</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-11.6</x:v>
+        <x:v>-9.2</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>228</x:v>
@@ -10522,10 +10522,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>228</x:v>
@@ -10551,10 +10551,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>1.08</x:v>
+        <x:v>0.98</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>-0.12</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>229</x:v>
@@ -10580,10 +10580,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>230</x:v>
@@ -10609,10 +10609,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>230</x:v>
@@ -10638,10 +10638,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>115.1</x:v>
+        <x:v>118.2</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>-3.1</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>230</x:v>
@@ -10667,10 +10667,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>8.35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.35</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>230</x:v>
@@ -10696,10 +10696,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>80.45</x:v>
+        <x:v>77.7</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>231</x:v>
@@ -10725,10 +10725,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>294</x:v>
+        <x:v>282.5</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>8.75</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>231</x:v>
@@ -10754,10 +10754,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>781.5</x:v>
+        <x:v>703.5</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>-86.5</x:v>
+        <x:v>-78</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>231</x:v>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -1127,10 +1127,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1156,10 +1156,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>13</x:v>
@@ -1188,7 +1188,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>16</x:v>
@@ -1214,10 +1214,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>16</x:v>
@@ -1243,10 +1243,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>16</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>20</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>20</x:v>
@@ -1330,10 +1330,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>20</x:v>
@@ -1359,10 +1359,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>20</x:v>
@@ -1388,10 +1388,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>20</x:v>
@@ -1420,7 +1420,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>25</x:v>
@@ -1446,10 +1446,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>27</x:v>
@@ -1475,10 +1475,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>28</x:v>
@@ -1504,10 +1504,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>29</x:v>
@@ -1533,10 +1533,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>29</x:v>
@@ -1562,10 +1562,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>7.79</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-0.86</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>29</x:v>
@@ -1591,10 +1591,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>40.52</x:v>
+        <x:v>37.86</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>-2.66</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>29</x:v>
@@ -1620,10 +1620,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>33</x:v>
@@ -1649,10 +1649,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>33</x:v>
@@ -1678,10 +1678,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>34</x:v>
@@ -1707,10 +1707,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>34</x:v>
@@ -1736,10 +1736,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>34</x:v>
@@ -1765,10 +1765,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>34</x:v>
@@ -1794,10 +1794,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>11.95</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>34</x:v>
@@ -1823,10 +1823,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>57.65</x:v>
+        <x:v>55.15</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-3.7</x:v>
+        <x:v>-2.5</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>37</x:v>
@@ -1852,10 +1852,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>14.39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>-0.39</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>39</x:v>
@@ -1881,10 +1881,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>9.09</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-0.43</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>41</x:v>
@@ -1910,10 +1910,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>37.6</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>43</x:v>
@@ -1939,10 +1939,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>45</x:v>
@@ -1968,10 +1968,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>55.35</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>-6.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>45</x:v>
@@ -1997,10 +1997,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>48</x:v>
@@ -2026,10 +2026,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>50</x:v>
@@ -2055,10 +2055,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>50</x:v>
@@ -2084,10 +2084,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>55.1</x:v>
+        <x:v>57.4</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>50</x:v>
@@ -2113,10 +2113,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>50</x:v>
@@ -2142,10 +2142,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>21.92</x:v>
+        <x:v>20.88</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>50</x:v>
@@ -2171,10 +2171,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>55</x:v>
@@ -2200,10 +2200,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>56</x:v>
@@ -2229,10 +2229,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>56</x:v>
@@ -2258,10 +2258,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>61.3</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>-6.8</x:v>
+        <x:v>-6.1</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>58</x:v>
@@ -2287,10 +2287,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>59</x:v>
@@ -2316,10 +2316,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>59</x:v>
@@ -2345,10 +2345,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>59</x:v>
@@ -2374,10 +2374,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>25.56</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>-2.22</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>61</x:v>
@@ -2403,10 +2403,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>40.52</x:v>
+        <x:v>37.86</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>-2.66</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>61</x:v>
@@ -2432,10 +2432,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>62</x:v>
@@ -2461,10 +2461,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>84.8</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-3.85</x:v>
+        <x:v>-4.8</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>62</x:v>
@@ -2490,10 +2490,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>649.5</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-22.5</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>65</x:v>
@@ -2519,10 +2519,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>66</x:v>
@@ -2548,10 +2548,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>66</x:v>
@@ -2577,10 +2577,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>68</x:v>
@@ -2606,10 +2606,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>68</x:v>
@@ -2635,10 +2635,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>20.84</x:v>
+        <x:v>19.88</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-2.26</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>70</x:v>
@@ -2664,10 +2664,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>11.95</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>70</x:v>
@@ -2693,10 +2693,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>40.52</x:v>
+        <x:v>37.86</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>-2.66</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>70</x:v>
@@ -2722,10 +2722,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>71</x:v>
@@ -2751,10 +2751,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>61.3</x:v>
+        <x:v>55.2</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-6.8</x:v>
+        <x:v>-6.1</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>71</x:v>
@@ -2780,10 +2780,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>649.5</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-22.5</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>72</x:v>
@@ -2809,10 +2809,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>72</x:v>
@@ -2838,10 +2838,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>72</x:v>
@@ -2867,10 +2867,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>72</x:v>
@@ -2896,10 +2896,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>75</x:v>
@@ -2925,10 +2925,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>14.39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>-0.39</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>76</x:v>
@@ -2954,10 +2954,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>9.5</x:v>
+        <x:v>9.01</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.61</x:v>
+        <x:v>-0.49</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>78</x:v>
@@ -2983,10 +2983,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>78</x:v>
@@ -3012,10 +3012,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>79</x:v>
@@ -3041,10 +3041,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>79</x:v>
@@ -3070,10 +3070,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>15.94</x:v>
+        <x:v>16.03</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.76</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>81</x:v>
@@ -3099,10 +3099,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>82</x:v>
@@ -3128,10 +3128,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>82</x:v>
@@ -3157,10 +3157,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>82</x:v>
@@ -3186,10 +3186,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>84</x:v>
@@ -3215,10 +3215,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>84</x:v>
@@ -3244,10 +3244,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>85</x:v>
@@ -3273,10 +3273,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>85</x:v>
@@ -3305,7 +3305,7 @@
         <x:v>2.88</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>-0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>87</x:v>
@@ -3331,10 +3331,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>89</x:v>
@@ -3360,10 +3360,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>89</x:v>
@@ -3389,10 +3389,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>89</x:v>
@@ -3418,10 +3418,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>89</x:v>
@@ -3447,10 +3447,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>90</x:v>
@@ -3476,10 +3476,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>40.52</x:v>
+        <x:v>37.86</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-4.5</x:v>
+        <x:v>-2.66</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>90</x:v>
@@ -3505,10 +3505,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>91</x:v>
@@ -3534,10 +3534,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>22.96</x:v>
+        <x:v>22.72</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>91</x:v>
@@ -3563,10 +3563,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>7.79</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-0.86</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>91</x:v>
@@ -3592,10 +3592,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>93</x:v>
@@ -3621,10 +3621,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>14.39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>-0.39</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>94</x:v>
@@ -3650,10 +3650,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>7.79</x:v>
+        <x:v>7.6</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>-0.86</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>94</x:v>
@@ -3682,7 +3682,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>94</x:v>
@@ -3711,7 +3711,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>95</x:v>
@@ -3737,10 +3737,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>61.4</x:v>
+        <x:v>61.15</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-3.65</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>95</x:v>
@@ -3766,10 +3766,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>95</x:v>
@@ -3795,10 +3795,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>98</x:v>
@@ -3824,10 +3824,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>98</x:v>
@@ -3856,7 +3856,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>99</x:v>
@@ -3882,10 +3882,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>99</x:v>
@@ -3911,10 +3911,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>11.95</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>99</x:v>
@@ -3940,10 +3940,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -3969,10 +3969,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>100</x:v>
@@ -3998,10 +3998,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>100</x:v>
@@ -4027,10 +4027,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>100</x:v>
@@ -4056,10 +4056,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>-1.43</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>100</x:v>
@@ -4085,10 +4085,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>102</x:v>
@@ -4114,10 +4114,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>102</x:v>
@@ -4143,10 +4143,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>102</x:v>
@@ -4172,10 +4172,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>103</x:v>
@@ -4201,10 +4201,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>103</x:v>
@@ -4230,10 +4230,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.33</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-0.89</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>103</x:v>
@@ -4262,7 +4262,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>105</x:v>
@@ -4288,10 +4288,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>105</x:v>
@@ -4317,10 +4317,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>105</x:v>
@@ -4346,10 +4346,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>105</x:v>
@@ -4375,10 +4375,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>105</x:v>
@@ -4404,10 +4404,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>106</x:v>
@@ -4433,10 +4433,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>118.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>-12.6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>106</x:v>
@@ -4462,10 +4462,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>5.76</x:v>
+        <x:v>5.64</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>109</x:v>
@@ -4491,10 +4491,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>109</x:v>
@@ -4520,10 +4520,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>111</x:v>
@@ -4549,10 +4549,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>112</x:v>
@@ -4578,10 +4578,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>112</x:v>
@@ -4607,10 +4607,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>112</x:v>
@@ -4636,10 +4636,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>113</x:v>
@@ -4665,10 +4665,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>114</x:v>
@@ -4694,10 +4694,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>115</x:v>
@@ -4723,10 +4723,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>115</x:v>
@@ -4752,10 +4752,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>117</x:v>
@@ -4781,10 +4781,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>117</x:v>
@@ -4810,10 +4810,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>118</x:v>
@@ -4839,10 +4839,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>15.94</x:v>
+        <x:v>16.03</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-0.76</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>119</x:v>
@@ -4868,10 +4868,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>14.98</x:v>
+        <x:v>14.64</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-0.87</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>119</x:v>
@@ -4897,10 +4897,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>9.09</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>-0.43</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>121</x:v>
@@ -4926,10 +4926,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>121</x:v>
@@ -4955,10 +4955,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>26.34</x:v>
+        <x:v>23.72</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-2.62</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>121</x:v>
@@ -4984,10 +4984,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>124</x:v>
@@ -5013,10 +5013,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>9.09</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.43</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>124</x:v>
@@ -5042,10 +5042,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>125</x:v>
@@ -5071,10 +5071,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>55.35</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-6.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>125</x:v>
@@ -5100,10 +5100,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>25.56</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>-2.22</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>126</x:v>
@@ -5132,7 +5132,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>126</x:v>
@@ -5158,10 +5158,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>127</x:v>
@@ -5187,10 +5187,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>128</x:v>
@@ -5216,10 +5216,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>128</x:v>
@@ -5245,10 +5245,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>128</x:v>
@@ -5274,10 +5274,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>128</x:v>
@@ -5303,10 +5303,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>129</x:v>
@@ -5332,10 +5332,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>26</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>131</x:v>
@@ -5361,10 +5361,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>132</x:v>
@@ -5393,7 +5393,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>133</x:v>
@@ -5419,10 +5419,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>133</x:v>
@@ -5448,10 +5448,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>134</x:v>
@@ -5477,10 +5477,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>135</x:v>
@@ -5506,10 +5506,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>649.5</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-22.5</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>135</x:v>
@@ -5535,10 +5535,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>135</x:v>
@@ -5564,10 +5564,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>135</x:v>
@@ -5593,10 +5593,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>55.35</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-6.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>136</x:v>
@@ -5622,10 +5622,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>137</x:v>
@@ -5651,10 +5651,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>137</x:v>
@@ -5680,10 +5680,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>137</x:v>
@@ -5709,10 +5709,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>138</x:v>
@@ -5738,10 +5738,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>139</x:v>
@@ -5767,10 +5767,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>118.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-12.6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>139</x:v>
@@ -5796,10 +5796,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>140</x:v>
@@ -5825,10 +5825,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>141</x:v>
@@ -5854,10 +5854,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>141</x:v>
@@ -5883,10 +5883,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>142</x:v>
@@ -5912,10 +5912,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>143</x:v>
@@ -5941,10 +5941,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>143</x:v>
@@ -5970,10 +5970,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>144</x:v>
@@ -5999,10 +5999,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>144</x:v>
@@ -6028,10 +6028,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>145</x:v>
@@ -6057,10 +6057,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>26</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>145</x:v>
@@ -6086,10 +6086,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>20.38</x:v>
+        <x:v>18.99</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>-2.26</x:v>
+        <x:v>-1.39</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>145</x:v>
@@ -6115,10 +6115,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>25.56</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>-2.22</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>147</x:v>
@@ -6144,10 +6144,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>147</x:v>
@@ -6173,10 +6173,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>147</x:v>
@@ -6202,10 +6202,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>3.38</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>147</x:v>
@@ -6231,10 +6231,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>118.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-12.6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>147</x:v>
@@ -6260,10 +6260,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>26</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>147</x:v>
@@ -6289,10 +6289,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>149</x:v>
@@ -6318,10 +6318,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>25.56</x:v>
+        <x:v>24.98</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>-2.22</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>149</x:v>
@@ -6347,10 +6347,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>149</x:v>
@@ -6376,10 +6376,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>150</x:v>
@@ -6405,10 +6405,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>151</x:v>
@@ -6434,10 +6434,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>151</x:v>
@@ -6463,10 +6463,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>151</x:v>
@@ -6492,10 +6492,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>152</x:v>
@@ -6521,10 +6521,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>152</x:v>
@@ -6550,10 +6550,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>26</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>152</x:v>
@@ -6579,10 +6579,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>153</x:v>
@@ -6608,10 +6608,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>153</x:v>
@@ -6637,10 +6637,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>154</x:v>
@@ -6666,10 +6666,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>154</x:v>
@@ -6695,10 +6695,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>154</x:v>
@@ -6724,10 +6724,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>649.5</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>-22.5</x:v>
+        <x:v>-4.5</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>155</x:v>
@@ -6753,10 +6753,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>155</x:v>
@@ -6782,10 +6782,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>155</x:v>
@@ -6811,10 +6811,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>155</x:v>
@@ -6843,7 +6843,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>156</x:v>
@@ -6869,10 +6869,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>156</x:v>
@@ -6898,10 +6898,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>156</x:v>
@@ -6927,10 +6927,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>156</x:v>
@@ -6956,10 +6956,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>157</x:v>
@@ -6985,10 +6985,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>33.38</x:v>
+        <x:v>31.18</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>-2.82</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>157</x:v>
@@ -7014,10 +7014,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>159</x:v>
@@ -7043,10 +7043,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>29.66</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>-3.28</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>161</x:v>
@@ -7072,10 +7072,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>162</x:v>
@@ -7104,7 +7104,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>162</x:v>
@@ -7130,10 +7130,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>162</x:v>
@@ -7159,10 +7159,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>162</x:v>
@@ -7188,10 +7188,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>3.15</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>162</x:v>
@@ -7217,10 +7217,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>3.15</x:v>
+        <x:v>3.14</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>162</x:v>
@@ -7246,10 +7246,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>164</x:v>
@@ -7275,10 +7275,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>164</x:v>
@@ -7304,10 +7304,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>164</x:v>
@@ -7333,10 +7333,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>10.95</x:v>
+        <x:v>10.99</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>166</x:v>
@@ -7362,10 +7362,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>10.95</x:v>
+        <x:v>10.99</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>166</x:v>
@@ -7391,10 +7391,10 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>10.95</x:v>
+        <x:v>10.99</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>166</x:v>
@@ -7420,10 +7420,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>166</x:v>
@@ -7449,10 +7449,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>168</x:v>
@@ -7478,10 +7478,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>168</x:v>
@@ -7507,10 +7507,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>169</x:v>
@@ -7539,7 +7539,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>170</x:v>
@@ -7565,10 +7565,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>170</x:v>
@@ -7594,10 +7594,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>170</x:v>
@@ -7623,10 +7623,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>3.38</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>170</x:v>
@@ -7652,10 +7652,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>3.38</x:v>
+        <x:v>3.31</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>-0.37</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>170</x:v>
@@ -7681,10 +7681,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>194.7</x:v>
+        <x:v>175.3</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>2</x:v>
+        <x:v>-19.4</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>172</x:v>
@@ -7713,7 +7713,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>172</x:v>
@@ -7739,10 +7739,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>173</x:v>
@@ -7768,10 +7768,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>173</x:v>
@@ -7797,10 +7797,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>173</x:v>
@@ -7826,10 +7826,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>174</x:v>
@@ -7855,10 +7855,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>174</x:v>
@@ -7884,10 +7884,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>32.36</x:v>
+        <x:v>31.84</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>174</x:v>
@@ -7913,10 +7913,10 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>17.18</x:v>
+        <x:v>16.97</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>174</x:v>
@@ -7942,10 +7942,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>177</x:v>
@@ -7974,7 +7974,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>177</x:v>
@@ -8000,10 +8000,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>178</x:v>
@@ -8029,10 +8029,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>75.2</x:v>
+        <x:v>73.85</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-1.35</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>180</x:v>
@@ -8058,10 +8058,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>180</x:v>
@@ -8087,10 +8087,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>181</x:v>
@@ -8116,10 +8116,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>181</x:v>
@@ -8145,10 +8145,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>181</x:v>
@@ -8174,10 +8174,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>181</x:v>
@@ -8203,10 +8203,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>181</x:v>
@@ -8232,10 +8232,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>15.1</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>181</x:v>
@@ -8261,10 +8261,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>181</x:v>
@@ -8290,10 +8290,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>181</x:v>
@@ -8319,10 +8319,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>183</x:v>
@@ -8348,10 +8348,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>183</x:v>
@@ -8380,7 +8380,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>183</x:v>
@@ -8406,10 +8406,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>33.38</x:v>
+        <x:v>31.18</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>-2.82</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>183</x:v>
@@ -8435,10 +8435,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>184</x:v>
@@ -8464,10 +8464,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>184</x:v>
@@ -8493,10 +8493,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>184</x:v>
@@ -8522,10 +8522,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>7.01</x:v>
+        <x:v>6.8</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>-0.59</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>186</x:v>
@@ -8551,10 +8551,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>187</x:v>
@@ -8580,10 +8580,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>187</x:v>
@@ -8609,10 +8609,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>26</x:v>
+        <x:v>27.24</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>-1.64</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>187</x:v>
@@ -8638,10 +8638,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>188</x:v>
@@ -8667,10 +8667,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>14.39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>-0.31</x:v>
+        <x:v>-0.39</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>188</x:v>
@@ -8696,10 +8696,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>189</x:v>
@@ -8725,10 +8725,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>190</x:v>
@@ -8754,10 +8754,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>190</x:v>
@@ -8783,10 +8783,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>190</x:v>
@@ -8812,10 +8812,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>15.1</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>191</x:v>
@@ -8841,10 +8841,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>192</x:v>
@@ -8870,10 +8870,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>11.95</x:v>
+        <x:v>11.36</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>-1.32</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>193</x:v>
@@ -8899,10 +8899,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>194</x:v>
@@ -8928,10 +8928,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B271" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>194</x:v>
@@ -8957,10 +8957,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B272" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>195</x:v>
@@ -8986,10 +8986,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>196</x:v>
@@ -9015,10 +9015,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>196</x:v>
@@ -9044,10 +9044,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>20.38</x:v>
+        <x:v>18.99</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>-2.26</x:v>
+        <x:v>-1.39</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>197</x:v>
@@ -9073,10 +9073,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>197</x:v>
@@ -9102,10 +9102,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.33</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>-0.89</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>198</x:v>
@@ -9131,10 +9131,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>4.21</x:v>
+        <x:v>4.06</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.15</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>199</x:v>
@@ -9160,10 +9160,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>199</x:v>
@@ -9189,10 +9189,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>-1.43</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>199</x:v>
@@ -9218,10 +9218,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>-1.43</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>199</x:v>
@@ -9247,10 +9247,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>200</x:v>
@@ -9276,10 +9276,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>12.82</x:v>
+        <x:v>12.77</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>200</x:v>
@@ -9308,7 +9308,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>200</x:v>
@@ -9334,10 +9334,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>202</x:v>
@@ -9363,10 +9363,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>203</x:v>
@@ -9395,7 +9395,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>204</x:v>
@@ -9421,10 +9421,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>55.35</x:v>
+        <x:v>55.65</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>-6.15</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>204</x:v>
@@ -9450,10 +9450,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>204</x:v>
@@ -9479,10 +9479,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>205</x:v>
@@ -9508,10 +9508,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>2.07</x:v>
+        <x:v>2.02</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.05</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>205</x:v>
@@ -9537,10 +9537,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>205</x:v>
@@ -9566,10 +9566,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>205</x:v>
@@ -9595,10 +9595,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>207</x:v>
@@ -9624,10 +9624,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>208</x:v>
@@ -9653,10 +9653,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>208</x:v>
@@ -9682,10 +9682,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>209</x:v>
@@ -9714,7 +9714,7 @@
         <x:v>54.5</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>1.35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>210</x:v>
@@ -9740,10 +9740,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>118.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>-12.6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>210</x:v>
@@ -9769,10 +9769,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>118.7</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>-12.6</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>210</x:v>
@@ -9798,10 +9798,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>2.2</x:v>
+        <x:v>2.04</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-0.16</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>212</x:v>
@@ -9827,10 +9827,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B302" s="0">
-        <x:v>20.84</x:v>
+        <x:v>19.88</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>-2.26</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>212</x:v>
@@ -9856,10 +9856,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>15.98</x:v>
+        <x:v>15.4</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.58</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>213</x:v>
@@ -9885,10 +9885,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>214</x:v>
@@ -9914,10 +9914,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>215</x:v>
@@ -9946,7 +9946,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>215</x:v>
@@ -9972,10 +9972,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>22.96</x:v>
+        <x:v>22.72</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>-1.08</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>216</x:v>
@@ -10001,10 +10001,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>29.5</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>-1.7</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>216</x:v>
@@ -10030,10 +10030,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>217</x:v>
@@ -10059,10 +10059,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>217</x:v>
@@ -10088,10 +10088,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>217</x:v>
@@ -10117,10 +10117,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>217</x:v>
@@ -10146,10 +10146,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>217</x:v>
@@ -10175,10 +10175,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="C314" s="0">
-        <x:v>-1.43</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
         <x:v>217</x:v>
@@ -10204,10 +10204,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>218</x:v>
@@ -10233,10 +10233,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15.1</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>-1.43</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>219</x:v>
@@ -10262,10 +10262,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>219</x:v>
@@ -10291,10 +10291,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>22.28</x:v>
+        <x:v>20.06</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>-2.46</x:v>
+        <x:v>-2.22</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>220</x:v>
@@ -10320,10 +10320,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>19.6</x:v>
+        <x:v>18.47</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.13</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>220</x:v>
@@ -10349,10 +10349,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>29.66</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>-3.28</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>220</x:v>
@@ -10378,10 +10378,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>367.25</x:v>
+        <x:v>338.5</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>-5</x:v>
+        <x:v>-28.75</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>221</x:v>
@@ -10407,10 +10407,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>221</x:v>
@@ -10436,10 +10436,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>9.09</x:v>
+        <x:v>8.75</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>-0.43</x:v>
+        <x:v>-0.34</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>221</x:v>
@@ -10465,10 +10465,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>221</x:v>
@@ -10494,10 +10494,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>20.84</x:v>
+        <x:v>19.88</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>-2.26</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>221</x:v>
@@ -10523,10 +10523,10 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>17.9</x:v>
+        <x:v>16.11</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-1.98</x:v>
+        <x:v>-1.79</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>223</x:v>
@@ -10552,10 +10552,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.33</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>-0.89</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>223</x:v>
@@ -10581,10 +10581,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>9.65</x:v>
+        <x:v>9.33</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>-0.89</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>223</x:v>
@@ -10610,10 +10610,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>3.31</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.21</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>223</x:v>
@@ -10639,10 +10639,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>10.99</x:v>
+        <x:v>11.1</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>-0.19</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>223</x:v>
@@ -10668,10 +10668,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>3.59</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>-0.39</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>225</x:v>
@@ -10697,10 +10697,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>10.93</x:v>
+        <x:v>10.83</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>-0.69</x:v>
+        <x:v>-0.1</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>225</x:v>
@@ -10726,10 +10726,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>225</x:v>
@@ -10755,10 +10755,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>8.25</x:v>
+        <x:v>7.89</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>0.02</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>227</x:v>
@@ -10784,10 +10784,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>29.66</x:v>
+        <x:v>27.88</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>-3.28</x:v>
+        <x:v>-1.78</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>227</x:v>
@@ -10813,10 +10813,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B336" s="0">
-        <x:v>1935</x:v>
+        <x:v>1742</x:v>
       </x:c>
       <x:c r="C336" s="0">
-        <x:v>-215</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
         <x:v>227</x:v>
@@ -10842,10 +10842,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B337" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C337" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
         <x:v>228</x:v>
@@ -10871,10 +10871,10 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B338" s="0">
-        <x:v>17.9</x:v>
+        <x:v>16.11</x:v>
       </x:c>
       <x:c r="C338" s="0">
-        <x:v>-1.98</x:v>
+        <x:v>-1.79</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
         <x:v>228</x:v>
@@ -10900,10 +10900,10 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B339" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C339" s="0">
-        <x:v>-0.3</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
         <x:v>228</x:v>
@@ -10929,10 +10929,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B340" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C340" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
         <x:v>228</x:v>
@@ -10961,7 +10961,7 @@
         <x:v>43.48</x:v>
       </x:c>
       <x:c r="C341" s="0">
-        <x:v>-3.04</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
         <x:v>228</x:v>
@@ -10987,10 +10987,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B342" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C342" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
         <x:v>228</x:v>
@@ -11016,10 +11016,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B343" s="0">
-        <x:v>25.34</x:v>
+        <x:v>24.8</x:v>
       </x:c>
       <x:c r="C343" s="0">
-        <x:v>-1.42</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
         <x:v>231</x:v>
@@ -11045,10 +11045,10 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B344" s="0">
-        <x:v>17.9</x:v>
+        <x:v>16.11</x:v>
       </x:c>
       <x:c r="C344" s="0">
-        <x:v>-1.98</x:v>
+        <x:v>-1.79</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
         <x:v>232</x:v>
@@ -11074,10 +11074,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B345" s="0">
-        <x:v>11.78</x:v>
+        <x:v>11.46</x:v>
       </x:c>
       <x:c r="C345" s="0">
-        <x:v>-1.28</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
         <x:v>233</x:v>
@@ -11103,10 +11103,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B346" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C346" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
         <x:v>233</x:v>
@@ -11132,10 +11132,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B347" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.68</x:v>
       </x:c>
       <x:c r="C347" s="0">
-        <x:v>-0.78</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
         <x:v>234</x:v>
@@ -11161,10 +11161,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B348" s="0">
-        <x:v>22.16</x:v>
+        <x:v>21.88</x:v>
       </x:c>
       <x:c r="C348" s="0">
-        <x:v>-0.68</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
         <x:v>235</x:v>
@@ -11190,10 +11190,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B349" s="0">
-        <x:v>4.09</x:v>
+        <x:v>4.49</x:v>
       </x:c>
       <x:c r="C349" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
         <x:v>237</x:v>
@@ -11219,10 +11219,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B350" s="0">
-        <x:v>74.45</x:v>
+        <x:v>73.25</x:v>
       </x:c>
       <x:c r="C350" s="0">
-        <x:v>-5.1</x:v>
+        <x:v>-1.2</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
         <x:v>238</x:v>
@@ -11248,10 +11248,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B351" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C351" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
         <x:v>238</x:v>
@@ -11277,10 +11277,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B352" s="0">
-        <x:v>0.59</x:v>
+        <x:v>0.58</x:v>
       </x:c>
       <x:c r="C352" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.01</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
         <x:v>239</x:v>
@@ -11306,10 +11306,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B353" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C353" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
         <x:v>240</x:v>
@@ -11335,10 +11335,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B354" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C354" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
         <x:v>240</x:v>
@@ -11364,10 +11364,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B355" s="0">
-        <x:v>92</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C355" s="0">
-        <x:v>-3.8</x:v>
+        <x:v>-2.35</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
         <x:v>240</x:v>
@@ -11393,10 +11393,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B356" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.92</x:v>
       </x:c>
       <x:c r="C356" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
         <x:v>240</x:v>
@@ -11422,10 +11422,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B357" s="0">
-        <x:v>64.35</x:v>
+        <x:v>62.1</x:v>
       </x:c>
       <x:c r="C357" s="0">
-        <x:v>-2.65</x:v>
+        <x:v>-2.25</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
         <x:v>241</x:v>
@@ -11451,10 +11451,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B358" s="0">
-        <x:v>235.2</x:v>
+        <x:v>211.7</x:v>
       </x:c>
       <x:c r="C358" s="0">
-        <x:v>-26.05</x:v>
+        <x:v>-23.5</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
         <x:v>241</x:v>
@@ -11480,10 +11480,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B359" s="0">
-        <x:v>246.2</x:v>
+        <x:v>221.6</x:v>
       </x:c>
       <x:c r="C359" s="0">
-        <x:v>-27.3</x:v>
+        <x:v>-24.6</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
         <x:v>241</x:v>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -1166,10 +1166,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1195,10 +1195,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>10</x:v>
@@ -1224,10 +1224,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
@@ -1253,10 +1253,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>15.61</x:v>
+        <x:v>15.57</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0.69</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>13</x:v>
@@ -1282,10 +1282,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>13</x:v>
@@ -1311,10 +1311,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1340,10 +1340,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1369,10 +1369,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>18</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>18</x:v>
@@ -1427,10 +1427,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>18</x:v>
@@ -1456,10 +1456,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>23.8</x:v>
+        <x:v>26.18</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>2.16</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>18</x:v>
@@ -1485,10 +1485,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>18</x:v>
@@ -1514,10 +1514,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>18</x:v>
@@ -1543,10 +1543,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>72.75</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>1.45</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>18</x:v>
@@ -1572,10 +1572,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>26</x:v>
@@ -1601,10 +1601,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>26</x:v>
@@ -1630,10 +1630,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>26</x:v>
@@ -1659,10 +1659,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>13.86</x:v>
+        <x:v>14.37</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>26</x:v>
@@ -1688,10 +1688,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>30</x:v>
@@ -1717,7 +1717,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>6.07</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>-0.03</x:v>
@@ -1746,10 +1746,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>30</x:v>
@@ -1775,10 +1775,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>30</x:v>
@@ -1804,10 +1804,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>18.73</x:v>
+        <x:v>19.7</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>30</x:v>
@@ -1833,10 +1833,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>1.97</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>30</x:v>
@@ -1865,7 +1865,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>37</x:v>
@@ -1891,10 +1891,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>37</x:v>
@@ -1920,7 +1920,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>6.07</x:v>
+        <x:v>6.04</x:v>
       </x:c>
       <x:c r="C28" s="0">
         <x:v>-0.03</x:v>
@@ -1949,10 +1949,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>38</x:v>
@@ -1978,10 +1978,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>40</x:v>
@@ -2007,10 +2007,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>42</x:v>
@@ -2036,10 +2036,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>42</x:v>
@@ -2065,10 +2065,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>42</x:v>
@@ -2094,10 +2094,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>44</x:v>
@@ -2123,10 +2123,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>44</x:v>
@@ -2152,10 +2152,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>44</x:v>
@@ -2181,10 +2181,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>44</x:v>
@@ -2210,10 +2210,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>44</x:v>
@@ -2239,10 +2239,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>47</x:v>
@@ -2268,10 +2268,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>49</x:v>
@@ -2297,10 +2297,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
@@ -2326,10 +2326,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>50</x:v>
@@ -2355,10 +2355,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>53</x:v>
@@ -2384,10 +2384,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>53</x:v>
@@ -2413,10 +2413,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>53</x:v>
@@ -2442,10 +2442,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>38.82</x:v>
+        <x:v>40.26</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>1.2</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>53</x:v>
@@ -2471,10 +2471,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>55</x:v>
@@ -2500,10 +2500,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>55</x:v>
@@ -2529,10 +2529,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>56</x:v>
@@ -2558,10 +2558,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>9.86</x:v>
+        <x:v>10.02</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>0.16</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>56</x:v>
@@ -2587,10 +2587,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>56</x:v>
@@ -2616,10 +2616,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>56</x:v>
@@ -2645,10 +2645,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>56</x:v>
@@ -2674,10 +2674,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>56</x:v>
@@ -2703,10 +2703,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>57.3</x:v>
+        <x:v>57.8</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>1.25</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>59</x:v>
@@ -2732,10 +2732,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>61</x:v>
@@ -2761,10 +2761,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>63</x:v>
@@ -2790,10 +2790,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>37.26</x:v>
+        <x:v>38.04</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>0.28</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>65</x:v>
@@ -2819,10 +2819,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>67</x:v>
@@ -2848,10 +2848,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>49.98</x:v>
+        <x:v>49.62</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>1.34</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>67</x:v>
@@ -2877,10 +2877,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>70</x:v>
@@ -2909,7 +2909,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>71</x:v>
@@ -2935,10 +2935,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.9</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.95</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>71</x:v>
@@ -2964,10 +2964,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>71</x:v>
@@ -2993,10 +2993,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>22.5</x:v>
+        <x:v>22.26</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>0.38</x:v>
+        <x:v>-0.24</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>71</x:v>
@@ -3022,10 +3022,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>71</x:v>
@@ -3051,10 +3051,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>76</x:v>
@@ -3083,7 +3083,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>77</x:v>
@@ -3109,10 +3109,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>77</x:v>
@@ -3138,10 +3138,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>71.65</x:v>
+        <x:v>78.8</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>6.5</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>79</x:v>
@@ -3170,7 +3170,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>80</x:v>
@@ -3196,10 +3196,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>80</x:v>
@@ -3225,10 +3225,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>80</x:v>
@@ -3254,10 +3254,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>81</x:v>
@@ -3283,10 +3283,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>38.82</x:v>
+        <x:v>40.26</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>1.2</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>81</x:v>
@@ -3312,10 +3312,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>102.4</x:v>
+        <x:v>100.6</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>2.1</x:v>
+        <x:v>-1.8</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>83</x:v>
@@ -3341,10 +3341,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>83</x:v>
@@ -3370,10 +3370,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>670.5</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>85</x:v>
@@ -3399,10 +3399,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>87</x:v>
@@ -3428,10 +3428,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>87</x:v>
@@ -3457,10 +3457,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>88</x:v>
@@ -3486,10 +3486,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>88</x:v>
@@ -3515,10 +3515,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>89</x:v>
@@ -3544,10 +3544,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>18.73</x:v>
+        <x:v>19.7</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>89</x:v>
@@ -3573,10 +3573,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>38.82</x:v>
+        <x:v>40.26</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>1.2</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>89</x:v>
@@ -3605,7 +3605,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>90</x:v>
@@ -3631,10 +3631,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>71.65</x:v>
+        <x:v>78.8</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>6.5</x:v>
+        <x:v>7.15</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>90</x:v>
@@ -3660,10 +3660,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>670.5</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>91</x:v>
@@ -3689,10 +3689,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>91</x:v>
@@ -3718,10 +3718,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>91</x:v>
@@ -3747,7 +3747,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C91" s="0">
         <x:v>0.04</x:v>
@@ -3776,10 +3776,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>93</x:v>
@@ -3805,10 +3805,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>94</x:v>
@@ -3834,10 +3834,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>12.39</x:v>
+        <x:v>11.85</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>0.26</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>96</x:v>
@@ -3863,10 +3863,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>96</x:v>
@@ -3892,10 +3892,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>97</x:v>
@@ -3921,10 +3921,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>97</x:v>
@@ -3950,10 +3950,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>15.58</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>99</x:v>
@@ -3979,10 +3979,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -4008,10 +4008,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>100</x:v>
@@ -4037,10 +4037,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>100</x:v>
@@ -4066,10 +4066,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>101</x:v>
@@ -4095,10 +4095,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>101</x:v>
@@ -4124,10 +4124,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>102</x:v>
@@ -4153,10 +4153,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>102</x:v>
@@ -4182,10 +4182,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>104</x:v>
@@ -4211,10 +4211,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>106</x:v>
@@ -4240,10 +4240,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>106</x:v>
@@ -4269,10 +4269,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>106</x:v>
@@ -4298,10 +4298,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>106</x:v>
@@ -4327,10 +4327,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>107</x:v>
@@ -4356,10 +4356,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>38.82</x:v>
+        <x:v>40.26</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1.2</x:v>
+        <x:v>1.44</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>107</x:v>
@@ -4385,10 +4385,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>23.06</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>0.46</x:v>
+        <x:v>0.74</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>109</x:v>
@@ -4414,10 +4414,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>109</x:v>
@@ -4443,10 +4443,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>109</x:v>
@@ -4472,10 +4472,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>110</x:v>
@@ -4501,10 +4501,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>111</x:v>
@@ -4530,10 +4530,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>8.33</x:v>
+        <x:v>8.24</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>111</x:v>
@@ -4559,10 +4559,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>111</x:v>
@@ -4588,10 +4588,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>62.3</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>1</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>113</x:v>
@@ -4617,10 +4617,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>113</x:v>
@@ -4646,10 +4646,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>113</x:v>
@@ -4675,10 +4675,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>115</x:v>
@@ -4704,10 +4704,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>115</x:v>
@@ -4733,10 +4733,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>116</x:v>
@@ -4762,10 +4762,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>116</x:v>
@@ -4791,10 +4791,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>116</x:v>
@@ -4823,7 +4823,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>117</x:v>
@@ -4849,10 +4849,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>117</x:v>
@@ -4878,10 +4878,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>117</x:v>
@@ -4907,10 +4907,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>117</x:v>
@@ -4936,10 +4936,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>15.04</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>117</x:v>
@@ -4965,10 +4965,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>119</x:v>
@@ -4994,10 +4994,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>119</x:v>
@@ -5023,10 +5023,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>119</x:v>
@@ -5052,10 +5052,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>120</x:v>
@@ -5081,10 +5081,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>9.17</x:v>
+        <x:v>9.59</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>120</x:v>
@@ -5110,10 +5110,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>120</x:v>
@@ -5139,10 +5139,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>122</x:v>
@@ -5168,10 +5168,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>122</x:v>
@@ -5197,10 +5197,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>122</x:v>
@@ -5226,7 +5226,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C142" s="0">
         <x:v>0.04</x:v>
@@ -5255,10 +5255,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>122</x:v>
@@ -5284,10 +5284,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>123</x:v>
@@ -5313,10 +5313,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>123</x:v>
@@ -5342,10 +5342,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>125</x:v>
@@ -5371,10 +5371,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>6.08</x:v>
+        <x:v>6.16</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>125</x:v>
@@ -5400,10 +5400,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>127</x:v>
@@ -5429,10 +5429,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>128</x:v>
@@ -5458,10 +5458,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>128</x:v>
@@ -5487,10 +5487,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>128</x:v>
@@ -5516,10 +5516,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>129</x:v>
@@ -5545,10 +5545,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>130</x:v>
@@ -5574,10 +5574,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>131</x:v>
@@ -5603,10 +5603,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>131</x:v>
@@ -5632,10 +5632,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>133</x:v>
@@ -5661,7 +5661,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C157" s="0">
         <x:v>0.04</x:v>
@@ -5690,10 +5690,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>134</x:v>
@@ -5719,10 +5719,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>15.58</x:v>
+        <x:v>15.71</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>135</x:v>
@@ -5748,10 +5748,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>13.99</x:v>
+        <x:v>14.34</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>135</x:v>
@@ -5777,10 +5777,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>137</x:v>
@@ -5806,10 +5806,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>23.8</x:v>
+        <x:v>26.18</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>2.16</x:v>
+        <x:v>2.38</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>137</x:v>
@@ -5835,10 +5835,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>137</x:v>
@@ -5864,10 +5864,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>139</x:v>
@@ -5893,10 +5893,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>139</x:v>
@@ -5922,10 +5922,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>140</x:v>
@@ -5951,10 +5951,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>49.98</x:v>
+        <x:v>49.62</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>1.34</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>140</x:v>
@@ -5980,10 +5980,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>141</x:v>
@@ -6009,10 +6009,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>141</x:v>
@@ -6038,10 +6038,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>142</x:v>
@@ -6067,10 +6067,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>143</x:v>
@@ -6096,10 +6096,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>143</x:v>
@@ -6125,10 +6125,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>143</x:v>
@@ -6154,10 +6154,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>143</x:v>
@@ -6183,10 +6183,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>144</x:v>
@@ -6212,10 +6212,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>146</x:v>
@@ -6241,10 +6241,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>147</x:v>
@@ -6270,10 +6270,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>148</x:v>
@@ -6299,10 +6299,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>148</x:v>
@@ -6328,10 +6328,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>149</x:v>
@@ -6357,10 +6357,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>150</x:v>
@@ -6386,10 +6386,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>670.5</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>150</x:v>
@@ -6415,10 +6415,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>150</x:v>
@@ -6444,10 +6444,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>150</x:v>
@@ -6473,10 +6473,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>49.98</x:v>
+        <x:v>49.62</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>1.34</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>151</x:v>
@@ -6502,10 +6502,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>152</x:v>
@@ -6531,10 +6531,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>152</x:v>
@@ -6560,10 +6560,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>152</x:v>
@@ -6589,10 +6589,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>153</x:v>
@@ -6618,7 +6618,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C190" s="0">
         <x:v>0.04</x:v>
@@ -6647,10 +6647,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>154</x:v>
@@ -6676,10 +6676,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>155</x:v>
@@ -6705,10 +6705,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>156</x:v>
@@ -6734,10 +6734,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>156</x:v>
@@ -6763,10 +6763,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>157</x:v>
@@ -6792,10 +6792,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>158</x:v>
@@ -6821,10 +6821,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>158</x:v>
@@ -6850,10 +6850,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>159</x:v>
@@ -6879,10 +6879,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B199" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>159</x:v>
@@ -6908,10 +6908,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>160</x:v>
@@ -6937,10 +6937,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>19.8</x:v>
+        <x:v>20.16</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>160</x:v>
@@ -6966,10 +6966,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>160</x:v>
@@ -6995,10 +6995,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>162</x:v>
@@ -7024,10 +7024,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>162</x:v>
@@ -7053,10 +7053,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>162</x:v>
@@ -7082,10 +7082,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>162</x:v>
@@ -7111,10 +7111,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>162</x:v>
@@ -7140,10 +7140,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B208" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>162</x:v>
@@ -7169,10 +7169,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>23.68</x:v>
+        <x:v>24.04</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>0.88</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>164</x:v>
@@ -7198,10 +7198,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>164</x:v>
@@ -7227,10 +7227,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>164</x:v>
@@ -7256,10 +7256,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>165</x:v>
@@ -7285,10 +7285,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>166</x:v>
@@ -7314,10 +7314,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>166</x:v>
@@ -7343,10 +7343,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>166</x:v>
@@ -7372,10 +7372,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>167</x:v>
@@ -7401,10 +7401,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>167</x:v>
@@ -7430,10 +7430,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>167</x:v>
@@ -7459,10 +7459,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>168</x:v>
@@ -7488,10 +7488,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>168</x:v>
@@ -7517,10 +7517,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>169</x:v>
@@ -7546,10 +7546,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>169</x:v>
@@ -7575,10 +7575,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B223" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>169</x:v>
@@ -7604,10 +7604,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>670.5</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>11.5</x:v>
+        <x:v>-11.5</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>170</x:v>
@@ -7633,10 +7633,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>170</x:v>
@@ -7662,10 +7662,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>170</x:v>
@@ -7691,10 +7691,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>170</x:v>
@@ -7720,10 +7720,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>171</x:v>
@@ -7749,10 +7749,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B229" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>171</x:v>
@@ -7778,10 +7778,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>171</x:v>
@@ -7807,10 +7807,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>171</x:v>
@@ -7836,10 +7836,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>172</x:v>
@@ -7865,10 +7865,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>28.4</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>172</x:v>
@@ -7894,10 +7894,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>174</x:v>
@@ -7923,10 +7923,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>175</x:v>
@@ -7952,10 +7952,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>176</x:v>
@@ -7981,10 +7981,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>102.1</x:v>
+        <x:v>106.1</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>6.8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>176</x:v>
@@ -8010,10 +8010,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B238" s="0">
-        <x:v>3.05</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>176</x:v>
@@ -8039,10 +8039,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>3.05</x:v>
+        <x:v>3.08</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>0.02</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>176</x:v>
@@ -8068,10 +8068,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>176</x:v>
@@ -8097,10 +8097,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>176</x:v>
@@ -8126,10 +8126,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>178</x:v>
@@ -8155,10 +8155,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>178</x:v>
@@ -8184,10 +8184,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>178</x:v>
@@ -8213,10 +8213,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>11.49</x:v>
+        <x:v>11.74</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>180</x:v>
@@ -8242,10 +8242,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>11.49</x:v>
+        <x:v>11.74</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>180</x:v>
@@ -8271,10 +8271,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>11.49</x:v>
+        <x:v>11.74</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>0.05</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>180</x:v>
@@ -8300,10 +8300,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>180</x:v>
@@ -8329,10 +8329,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>182</x:v>
@@ -8358,10 +8358,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>182</x:v>
@@ -8387,10 +8387,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>183</x:v>
@@ -8416,10 +8416,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B252" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>184</x:v>
@@ -8445,10 +8445,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>184</x:v>
@@ -8474,10 +8474,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>3.29</x:v>
+        <x:v>3.35</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>184</x:v>
@@ -8503,10 +8503,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>184</x:v>
@@ -8532,10 +8532,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>184</x:v>
@@ -8561,10 +8561,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>137.8</x:v>
+        <x:v>151.5</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>12.5</x:v>
+        <x:v>13.7</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>186</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>186</x:v>
@@ -8619,10 +8619,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>187</x:v>
@@ -8648,10 +8648,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>187</x:v>
@@ -8677,10 +8677,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>187</x:v>
@@ -8706,10 +8706,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>188</x:v>
@@ -8735,10 +8735,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>188</x:v>
@@ -8764,10 +8764,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>33.38</x:v>
+        <x:v>34.26</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>0.94</x:v>
+        <x:v>0.88</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>188</x:v>
@@ -8793,10 +8793,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>16.35</x:v>
+        <x:v>16.62</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>188</x:v>
@@ -8822,10 +8822,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>191</x:v>
@@ -8851,10 +8851,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>191</x:v>
@@ -8880,10 +8880,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>192</x:v>
@@ -8909,10 +8909,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>82.2</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>1.2</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>194</x:v>
@@ -8938,10 +8938,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>194</x:v>
@@ -8970,7 +8970,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>195</x:v>
@@ -8999,7 +8999,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>195</x:v>
@@ -9025,10 +9025,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>195</x:v>
@@ -9054,10 +9054,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>15.61</x:v>
+        <x:v>15.57</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>0.69</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>195</x:v>
@@ -9083,10 +9083,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>195</x:v>
@@ -9112,10 +9112,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>195</x:v>
@@ -9141,10 +9141,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>195</x:v>
@@ -9170,10 +9170,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>195</x:v>
@@ -9199,10 +9199,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>196</x:v>
@@ -9228,10 +9228,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>196</x:v>
@@ -9257,10 +9257,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>28.4</x:v>
+        <x:v>28.78</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>196</x:v>
@@ -9286,10 +9286,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>196</x:v>
@@ -9315,10 +9315,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>197</x:v>
@@ -9344,10 +9344,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B284" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>197</x:v>
@@ -9373,10 +9373,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>197</x:v>
@@ -9402,10 +9402,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>7.04</x:v>
+        <x:v>7.23</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>0.15</x:v>
+        <x:v>0.19</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>199</x:v>
@@ -9431,10 +9431,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B287" s="0">
-        <x:v>29.42</x:v>
+        <x:v>30.26</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>0.6</x:v>
+        <x:v>0.84</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>200</x:v>
@@ -9460,10 +9460,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>200</x:v>
@@ -9489,10 +9489,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>200</x:v>
@@ -9518,10 +9518,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>201</x:v>
@@ -9547,10 +9547,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>14</x:v>
+        <x:v>14.03</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>-0.33</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>201</x:v>
@@ -9576,10 +9576,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>202</x:v>
@@ -9605,10 +9605,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>203</x:v>
@@ -9634,10 +9634,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>203</x:v>
@@ -9663,10 +9663,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>203</x:v>
@@ -9692,10 +9692,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>15.61</x:v>
+        <x:v>15.57</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>0.69</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>204</x:v>
@@ -9721,10 +9721,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>205</x:v>
@@ -9750,10 +9750,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B298" s="0">
-        <x:v>11.55</x:v>
+        <x:v>12.1</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>0.09</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>206</x:v>
@@ -9779,10 +9779,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>207</x:v>
@@ -9808,10 +9808,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>207</x:v>
@@ -9837,10 +9837,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>208</x:v>
@@ -9869,7 +9869,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>209</x:v>
@@ -9895,10 +9895,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>209</x:v>
@@ -9924,10 +9924,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>19.8</x:v>
+        <x:v>20.16</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>0.19</x:v>
+        <x:v>0.36</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>210</x:v>
@@ -9953,10 +9953,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>210</x:v>
@@ -9982,10 +9982,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B306" s="0">
-        <x:v>9.17</x:v>
+        <x:v>9.59</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>211</x:v>
@@ -10011,10 +10011,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.19</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>212</x:v>
@@ -10040,10 +10040,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>212</x:v>
@@ -10069,10 +10069,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>15.04</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>212</x:v>
@@ -10098,10 +10098,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>15.04</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>212</x:v>
@@ -10127,10 +10127,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>213</x:v>
@@ -10156,10 +10156,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>213</x:v>
@@ -10185,10 +10185,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>12.91</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>0.82</x:v>
+        <x:v>0.99</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>213</x:v>
@@ -10214,7 +10214,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C314" s="0">
         <x:v>0.04</x:v>
@@ -10243,10 +10243,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>216</x:v>
@@ -10272,10 +10272,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>217</x:v>
@@ -10301,10 +10301,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>217</x:v>
@@ -10330,10 +10330,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>49.98</x:v>
+        <x:v>49.62</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>1.34</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>217</x:v>
@@ -10359,10 +10359,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>218</x:v>
@@ -10388,10 +10388,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>1.94</x:v>
+        <x:v>1.99</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>218</x:v>
@@ -10417,10 +10417,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>218</x:v>
@@ -10446,10 +10446,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>218</x:v>
@@ -10475,10 +10475,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>220</x:v>
@@ -10504,10 +10504,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>221</x:v>
@@ -10533,10 +10533,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>221</x:v>
@@ -10562,10 +10562,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>222</x:v>
@@ -10591,10 +10591,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>53.3</x:v>
+        <x:v>53.7</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>0.3</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>223</x:v>
@@ -10620,10 +10620,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>223</x:v>
@@ -10649,10 +10649,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>123.8</x:v>
+        <x:v>123.3</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>0.1</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>223</x:v>
@@ -10678,10 +10678,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>2.03</x:v>
+        <x:v>2.09</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.06</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>225</x:v>
@@ -10707,10 +10707,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>18.73</x:v>
+        <x:v>19.7</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>225</x:v>
@@ -10736,10 +10736,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>15.4</x:v>
+        <x:v>15.81</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>226</x:v>
@@ -10765,10 +10765,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>227</x:v>
@@ -10794,10 +10794,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>228</x:v>
@@ -10823,10 +10823,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>228</x:v>
@@ -10852,10 +10852,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B336" s="0">
-        <x:v>23.06</x:v>
+        <x:v>23.8</x:v>
       </x:c>
       <x:c r="C336" s="0">
-        <x:v>0.46</x:v>
+        <x:v>0.74</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
         <x:v>229</x:v>
@@ -10881,10 +10881,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B337" s="0">
-        <x:v>27.62</x:v>
+        <x:v>27.96</x:v>
       </x:c>
       <x:c r="C337" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
         <x:v>229</x:v>
@@ -10910,10 +10910,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B338" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C338" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
         <x:v>230</x:v>
@@ -10939,10 +10939,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B339" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C339" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
         <x:v>230</x:v>
@@ -10968,10 +10968,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B340" s="0">
-        <x:v>15.04</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="C340" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
         <x:v>230</x:v>
@@ -10997,10 +10997,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B341" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C341" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
         <x:v>230</x:v>
@@ -11026,10 +11026,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B342" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C342" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
         <x:v>230</x:v>
@@ -11055,10 +11055,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B343" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C343" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
         <x:v>230</x:v>
@@ -11084,10 +11084,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B344" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C344" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
         <x:v>231</x:v>
@@ -11113,10 +11113,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B345" s="0">
-        <x:v>15.04</x:v>
+        <x:v>15.36</x:v>
       </x:c>
       <x:c r="C345" s="0">
-        <x:v>0.2</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
         <x:v>232</x:v>
@@ -11142,10 +11142,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B346" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C346" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
         <x:v>232</x:v>
@@ -11171,10 +11171,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B347" s="0">
-        <x:v>20.12</x:v>
+        <x:v>20.9</x:v>
       </x:c>
       <x:c r="C347" s="0">
-        <x:v>0.04</x:v>
+        <x:v>0.78</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
         <x:v>233</x:v>
@@ -11200,10 +11200,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B348" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="C348" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
         <x:v>233</x:v>
@@ -11229,10 +11229,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B349" s="0">
-        <x:v>19.29</x:v>
+        <x:v>19.07</x:v>
       </x:c>
       <x:c r="C349" s="0">
-        <x:v>1.21</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
         <x:v>233</x:v>
@@ -11258,10 +11258,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B350" s="0">
-        <x:v>348.75</x:v>
+        <x:v>351.25</x:v>
       </x:c>
       <x:c r="C350" s="0">
-        <x:v>0</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
         <x:v>234</x:v>
@@ -11287,10 +11287,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B351" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C351" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
         <x:v>234</x:v>
@@ -11316,10 +11316,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B352" s="0">
-        <x:v>8.64</x:v>
+        <x:v>8.88</x:v>
       </x:c>
       <x:c r="C352" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
         <x:v>234</x:v>
@@ -11345,10 +11345,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B353" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C353" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
         <x:v>234</x:v>
@@ -11374,10 +11374,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B354" s="0">
-        <x:v>18.73</x:v>
+        <x:v>19.7</x:v>
       </x:c>
       <x:c r="C354" s="0">
-        <x:v>-0.58</x:v>
+        <x:v>0.97</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
         <x:v>234</x:v>
@@ -11403,10 +11403,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B355" s="0">
-        <x:v>9.17</x:v>
+        <x:v>9.59</x:v>
       </x:c>
       <x:c r="C355" s="0">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
         <x:v>235</x:v>
@@ -11432,10 +11432,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B356" s="0">
-        <x:v>9.17</x:v>
+        <x:v>9.59</x:v>
       </x:c>
       <x:c r="C356" s="0">
-        <x:v>0</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
         <x:v>235</x:v>
@@ -11461,10 +11461,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B357" s="0">
-        <x:v>14.8</x:v>
+        <x:v>16.28</x:v>
       </x:c>
       <x:c r="C357" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
         <x:v>235</x:v>
@@ -11490,10 +11490,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B358" s="0">
-        <x:v>3.66</x:v>
+        <x:v>3.64</x:v>
       </x:c>
       <x:c r="C358" s="0">
-        <x:v>-0.14</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
         <x:v>235</x:v>
@@ -11519,10 +11519,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B359" s="0">
-        <x:v>12.45</x:v>
+        <x:v>12.57</x:v>
       </x:c>
       <x:c r="C359" s="0">
-        <x:v>-0.65</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
         <x:v>235</x:v>
@@ -11548,10 +11548,10 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B360" s="0">
-        <x:v>10.12</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="C360" s="0">
-        <x:v>0.01</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="D360" s="0" t="s">
         <x:v>239</x:v>
@@ -11577,10 +11577,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B361" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C361" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D361" s="0" t="s">
         <x:v>239</x:v>
@@ -11606,7 +11606,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B362" s="0">
-        <x:v>3.65</x:v>
+        <x:v>3.69</x:v>
       </x:c>
       <x:c r="C362" s="0">
         <x:v>0.04</x:v>
@@ -11635,10 +11635,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B363" s="0">
-        <x:v>8.76</x:v>
+        <x:v>9.57</x:v>
       </x:c>
       <x:c r="C363" s="0">
-        <x:v>0.13</x:v>
+        <x:v>0.81</x:v>
       </x:c>
       <x:c r="D363" s="0" t="s">
         <x:v>240</x:v>
@@ -11664,10 +11664,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B364" s="0">
-        <x:v>29.3</x:v>
+        <x:v>29.62</x:v>
       </x:c>
       <x:c r="C364" s="0">
-        <x:v>0.14</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="D364" s="0" t="s">
         <x:v>240</x:v>
@@ -11693,10 +11693,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B365" s="0">
-        <x:v>834.5</x:v>
+        <x:v>751.5</x:v>
       </x:c>
       <x:c r="C365" s="0">
-        <x:v>-92.5</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="D365" s="0" t="s">
         <x:v>240</x:v>
@@ -11722,10 +11722,10 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B366" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C366" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D366" s="0" t="s">
         <x:v>242</x:v>
@@ -11751,10 +11751,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B367" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C367" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D367" s="0" t="s">
         <x:v>242</x:v>
@@ -11780,10 +11780,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B368" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C368" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D368" s="0" t="s">
         <x:v>242</x:v>
@@ -11809,10 +11809,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B369" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C369" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D369" s="0" t="s">
         <x:v>242</x:v>
@@ -11838,10 +11838,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B370" s="0">
-        <x:v>14.8</x:v>
+        <x:v>16.28</x:v>
       </x:c>
       <x:c r="C370" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="D370" s="0" t="s">
         <x:v>242</x:v>
@@ -11867,10 +11867,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B371" s="0">
-        <x:v>40.7</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C371" s="0">
-        <x:v>0.8</x:v>
+        <x:v>1.24</x:v>
       </x:c>
       <x:c r="D371" s="0" t="s">
         <x:v>242</x:v>
@@ -11896,10 +11896,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B372" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.72</x:v>
       </x:c>
       <x:c r="C372" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D372" s="0" t="s">
         <x:v>244</x:v>
@@ -11925,10 +11925,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B373" s="0">
-        <x:v>14.8</x:v>
+        <x:v>16.28</x:v>
       </x:c>
       <x:c r="C373" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="D373" s="0" t="s">
         <x:v>245</x:v>
@@ -11957,7 +11957,7 @@
         <x:v>10.4</x:v>
       </x:c>
       <x:c r="C374" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D374" s="0" t="s">
         <x:v>246</x:v>
@@ -11983,10 +11983,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B375" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C375" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
         <x:v>246</x:v>
@@ -12012,10 +12012,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B376" s="0">
-        <x:v>12.82</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C376" s="0">
-        <x:v>0.21</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
         <x:v>247</x:v>
@@ -12041,10 +12041,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B377" s="0">
-        <x:v>22.7</x:v>
+        <x:v>23.16</x:v>
       </x:c>
       <x:c r="C377" s="0">
-        <x:v>0.7</x:v>
+        <x:v>0.46</x:v>
       </x:c>
       <x:c r="D377" s="0" t="s">
         <x:v>248</x:v>
@@ -12070,10 +12070,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B378" s="0">
-        <x:v>3.28</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="C378" s="0">
-        <x:v>-0.01</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="D378" s="0" t="s">
         <x:v>250</x:v>
@@ -12099,10 +12099,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B379" s="0">
-        <x:v>71.45</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C379" s="0">
-        <x:v>1.55</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="D379" s="0" t="s">
         <x:v>251</x:v>
@@ -12128,10 +12128,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B380" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C380" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D380" s="0" t="s">
         <x:v>251</x:v>
@@ -12157,10 +12157,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B381" s="0">
-        <x:v>0.73</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="C381" s="0">
-        <x:v>0.06</x:v>
+        <x:v>0.07</x:v>
       </x:c>
       <x:c r="D381" s="0" t="s">
         <x:v>252</x:v>
@@ -12186,10 +12186,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B382" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C382" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D382" s="0" t="s">
         <x:v>253</x:v>
@@ -12215,10 +12215,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B383" s="0">
-        <x:v>89.9</x:v>
+        <x:v>89.65</x:v>
       </x:c>
       <x:c r="C383" s="0">
-        <x:v>-3.35</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="D383" s="0" t="s">
         <x:v>253</x:v>
@@ -12244,10 +12244,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B384" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C384" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D384" s="0" t="s">
         <x:v>253</x:v>
@@ -12273,10 +12273,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B385" s="0">
-        <x:v>4.85</x:v>
+        <x:v>5.03</x:v>
       </x:c>
       <x:c r="C385" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="D385" s="0" t="s">
         <x:v>253</x:v>
@@ -12302,10 +12302,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B386" s="0">
-        <x:v>197.5</x:v>
+        <x:v>204.4</x:v>
       </x:c>
       <x:c r="C386" s="0">
-        <x:v>12.6</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D386" s="0" t="s">
         <x:v>254</x:v>
@@ -12331,10 +12331,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B387" s="0">
-        <x:v>64.65</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="C387" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>2.45</x:v>
       </x:c>
       <x:c r="D387" s="0" t="s">
         <x:v>254</x:v>
@@ -12360,10 +12360,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B388" s="0">
-        <x:v>106.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C388" s="0">
-        <x:v>-11.8</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D388" s="0" t="s">
         <x:v>254</x:v>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -1166,10 +1166,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1195,10 +1195,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>10</x:v>
@@ -1224,10 +1224,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>13</x:v>
@@ -1253,10 +1253,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-0.57</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>13</x:v>
@@ -1282,10 +1282,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>12.1</x:v>
+        <x:v>11.28</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0.55</x:v>
+        <x:v>-0.82</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>13</x:v>
@@ -1311,10 +1311,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1340,10 +1340,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1369,10 +1369,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>18</x:v>
@@ -1398,10 +1398,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>24.04</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>18</x:v>
@@ -1427,10 +1427,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>18</x:v>
@@ -1456,10 +1456,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>26.18</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>2.38</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>18</x:v>
@@ -1485,10 +1485,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>18</x:v>
@@ -1514,10 +1514,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>18</x:v>
@@ -1543,10 +1543,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>75</x:v>
+        <x:v>72.05</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>2.25</x:v>
+        <x:v>-2.95</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>18</x:v>
@@ -1572,10 +1572,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>26</x:v>
@@ -1601,10 +1601,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>26</x:v>
@@ -1630,10 +1630,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>26</x:v>
@@ -1659,10 +1659,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>14.37</x:v>
+        <x:v>13.9</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0.51</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>26</x:v>
@@ -1688,10 +1688,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>30</x:v>
@@ -1717,10 +1717,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>6.04</x:v>
+        <x:v>5.85</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-0.03</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>30</x:v>
@@ -1746,10 +1746,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>30</x:v>
@@ -1775,10 +1775,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>30</x:v>
@@ -1804,10 +1804,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>19.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0.97</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>30</x:v>
@@ -1833,10 +1833,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>2.03</x:v>
+        <x:v>1.83</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>30</x:v>
@@ -1862,10 +1862,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>37</x:v>
@@ -1891,10 +1891,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>37</x:v>
@@ -1920,10 +1920,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>6.04</x:v>
+        <x:v>5.85</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-0.03</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>38</x:v>
@@ -1949,10 +1949,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>38</x:v>
@@ -1978,10 +1978,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>40</x:v>
@@ -2007,10 +2007,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>42</x:v>
@@ -2036,10 +2036,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>42</x:v>
@@ -2065,10 +2065,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>42</x:v>
@@ -2094,10 +2094,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>44</x:v>
@@ -2123,10 +2123,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>44</x:v>
@@ -2152,10 +2152,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>44</x:v>
@@ -2181,10 +2181,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>44</x:v>
@@ -2210,10 +2210,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>44</x:v>
@@ -2239,10 +2239,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>47</x:v>
@@ -2268,10 +2268,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>49</x:v>
@@ -2297,10 +2297,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>50</x:v>
@@ -2326,10 +2326,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>50</x:v>
@@ -2355,10 +2355,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>8.24</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>53</x:v>
@@ -2384,10 +2384,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>53</x:v>
@@ -2413,10 +2413,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>53</x:v>
@@ -2442,10 +2442,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>40.26</x:v>
+        <x:v>38.66</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>1.44</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>53</x:v>
@@ -2471,10 +2471,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>55</x:v>
@@ -2500,10 +2500,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>55</x:v>
@@ -2529,10 +2529,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>56</x:v>
@@ -2558,10 +2558,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>10.02</x:v>
+        <x:v>9.76</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>0.16</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>56</x:v>
@@ -2587,10 +2587,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>12.1</x:v>
+        <x:v>11.28</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>0.55</x:v>
+        <x:v>-0.82</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>56</x:v>
@@ -2616,10 +2616,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>56</x:v>
@@ -2645,10 +2645,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>56</x:v>
@@ -2674,10 +2674,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>56</x:v>
@@ -2703,10 +2703,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>57.8</x:v>
+        <x:v>56.95</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>0.5</x:v>
+        <x:v>-0.85</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>59</x:v>
@@ -2732,10 +2732,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>61</x:v>
@@ -2761,10 +2761,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>63</x:v>
@@ -2790,10 +2790,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>38.04</x:v>
+        <x:v>36.54</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.5</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>65</x:v>
@@ -2819,10 +2819,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>67</x:v>
@@ -2848,10 +2848,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>49.62</x:v>
+        <x:v>48.96</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>67</x:v>
@@ -2877,10 +2877,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>70</x:v>
@@ -2906,10 +2906,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>71</x:v>
@@ -2935,10 +2935,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>54.9</x:v>
+        <x:v>54.1</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>0.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>71</x:v>
@@ -2964,10 +2964,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>71</x:v>
@@ -2993,10 +2993,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>22.26</x:v>
+        <x:v>21.78</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.24</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>71</x:v>
@@ -3022,10 +3022,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>71</x:v>
@@ -3051,10 +3051,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>76</x:v>
@@ -3080,10 +3080,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>77</x:v>
@@ -3109,10 +3109,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>77</x:v>
@@ -3138,10 +3138,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>78.8</x:v>
+        <x:v>86.45</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>7.15</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>79</x:v>
@@ -3167,10 +3167,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>80</x:v>
@@ -3196,10 +3196,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>80</x:v>
@@ -3225,10 +3225,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>80</x:v>
@@ -3254,10 +3254,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>24.04</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>81</x:v>
@@ -3283,10 +3283,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>40.26</x:v>
+        <x:v>38.66</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>1.44</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>81</x:v>
@@ -3312,10 +3312,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>100.6</x:v>
+        <x:v>94.5</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-1.8</x:v>
+        <x:v>-6.1</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>83</x:v>
@@ -3341,10 +3341,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>83</x:v>
@@ -3370,10 +3370,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>659</x:v>
+        <x:v>658.5</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-11.5</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>85</x:v>
@@ -3399,10 +3399,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>87</x:v>
@@ -3428,10 +3428,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>87</x:v>
@@ -3457,10 +3457,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>88</x:v>
@@ -3486,10 +3486,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>88</x:v>
@@ -3515,10 +3515,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>12.1</x:v>
+        <x:v>11.28</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>0.55</x:v>
+        <x:v>-0.82</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>89</x:v>
@@ -3544,10 +3544,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>19.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>0.97</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>89</x:v>
@@ -3573,10 +3573,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>40.26</x:v>
+        <x:v>38.66</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>1.44</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>89</x:v>
@@ -3602,10 +3602,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>90</x:v>
@@ -3631,10 +3631,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>78.8</x:v>
+        <x:v>86.45</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>7.15</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>90</x:v>
@@ -3660,10 +3660,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>659</x:v>
+        <x:v>658.5</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-11.5</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>91</x:v>
@@ -3689,10 +3689,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>91</x:v>
@@ -3718,10 +3718,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>91</x:v>
@@ -3747,10 +3747,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>91</x:v>
@@ -3776,10 +3776,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>93</x:v>
@@ -3805,10 +3805,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>94</x:v>
@@ -3834,10 +3834,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>11.85</x:v>
+        <x:v>11.21</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-0.54</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>96</x:v>
@@ -3863,10 +3863,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>96</x:v>
@@ -3892,10 +3892,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>97</x:v>
@@ -3921,10 +3921,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>97</x:v>
@@ -3950,10 +3950,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>0.13</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>99</x:v>
@@ -3979,10 +3979,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -4008,10 +4008,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>100</x:v>
@@ -4037,10 +4037,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>100</x:v>
@@ -4066,10 +4066,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>101</x:v>
@@ -4095,10 +4095,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>101</x:v>
@@ -4124,10 +4124,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>102</x:v>
@@ -4153,10 +4153,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>102</x:v>
@@ -4182,10 +4182,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.07</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>104</x:v>
@@ -4211,10 +4211,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>106</x:v>
@@ -4240,10 +4240,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>106</x:v>
@@ -4269,10 +4269,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>106</x:v>
@@ -4298,10 +4298,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>106</x:v>
@@ -4327,10 +4327,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>107</x:v>
@@ -4356,10 +4356,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>40.26</x:v>
+        <x:v>38.66</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>1.44</x:v>
+        <x:v>-1.6</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>107</x:v>
@@ -4385,10 +4385,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>23.8</x:v>
+        <x:v>22.9</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>0.74</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>109</x:v>
@@ -4414,10 +4414,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>8.24</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>109</x:v>
@@ -4443,10 +4443,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>109</x:v>
@@ -4472,10 +4472,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>110</x:v>
@@ -4501,10 +4501,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>111</x:v>
@@ -4530,10 +4530,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>8.24</x:v>
+        <x:v>8.04</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>111</x:v>
@@ -4559,10 +4559,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>111</x:v>
@@ -4588,10 +4588,10 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>62.8</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>0.5</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>113</x:v>
@@ -4617,10 +4617,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>113</x:v>
@@ -4646,10 +4646,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>113</x:v>
@@ -4675,10 +4675,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>115</x:v>
@@ -4704,10 +4704,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>115</x:v>
@@ -4733,10 +4733,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>116</x:v>
@@ -4762,10 +4762,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>12.1</x:v>
+        <x:v>11.28</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>0.55</x:v>
+        <x:v>-0.82</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>116</x:v>
@@ -4791,10 +4791,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>116</x:v>
@@ -4820,10 +4820,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>117</x:v>
@@ -4849,10 +4849,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>117</x:v>
@@ -4878,10 +4878,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>117</x:v>
@@ -4907,10 +4907,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>117</x:v>
@@ -4936,10 +4936,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>117</x:v>
@@ -4965,10 +4965,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>119</x:v>
@@ -4994,10 +4994,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>119</x:v>
@@ -5023,10 +5023,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>119</x:v>
@@ -5052,10 +5052,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>120</x:v>
@@ -5081,10 +5081,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>9.59</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>0.42</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>120</x:v>
@@ -5110,10 +5110,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>120</x:v>
@@ -5139,10 +5139,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>122</x:v>
@@ -5168,10 +5168,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>122</x:v>
@@ -5197,10 +5197,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>122</x:v>
@@ -5226,10 +5226,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>122</x:v>
@@ -5255,10 +5255,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>122</x:v>
@@ -5284,10 +5284,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>123</x:v>
@@ -5313,10 +5313,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>123</x:v>
@@ -5342,10 +5342,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>125</x:v>
@@ -5371,10 +5371,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>6.16</x:v>
+        <x:v>5.99</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>0.08</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>125</x:v>
@@ -5400,10 +5400,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>127</x:v>
@@ -5429,10 +5429,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>128</x:v>
@@ -5458,10 +5458,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>128</x:v>
@@ -5487,10 +5487,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>128</x:v>
@@ -5516,10 +5516,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>129</x:v>
@@ -5545,10 +5545,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>130</x:v>
@@ -5574,10 +5574,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>131</x:v>
@@ -5603,10 +5603,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>131</x:v>
@@ -5632,10 +5632,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>133</x:v>
@@ -5661,10 +5661,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>133</x:v>
@@ -5690,10 +5690,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>134</x:v>
@@ -5719,10 +5719,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>15.71</x:v>
+        <x:v>15.19</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>0.13</x:v>
+        <x:v>-0.52</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>135</x:v>
@@ -5748,10 +5748,10 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>14.34</x:v>
+        <x:v>13.87</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>0.35</x:v>
+        <x:v>-0.47</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>135</x:v>
@@ -5777,10 +5777,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>137</x:v>
@@ -5806,10 +5806,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>26.18</x:v>
+        <x:v>25.7</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>2.38</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>137</x:v>
@@ -5835,10 +5835,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>137</x:v>
@@ -5864,10 +5864,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>139</x:v>
@@ -5893,10 +5893,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>139</x:v>
@@ -5922,10 +5922,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>140</x:v>
@@ -5951,10 +5951,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>49.62</x:v>
+        <x:v>48.96</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>140</x:v>
@@ -5980,10 +5980,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>24.04</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>141</x:v>
@@ -6009,10 +6009,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>141</x:v>
@@ -6038,10 +6038,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>142</x:v>
@@ -6067,10 +6067,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>143</x:v>
@@ -6096,10 +6096,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>143</x:v>
@@ -6125,10 +6125,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>143</x:v>
@@ -6154,10 +6154,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>143</x:v>
@@ -6183,10 +6183,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>144</x:v>
@@ -6212,10 +6212,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>146</x:v>
@@ -6241,10 +6241,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>147</x:v>
@@ -6270,10 +6270,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>148</x:v>
@@ -6299,10 +6299,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>148</x:v>
@@ -6328,10 +6328,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>149</x:v>
@@ -6357,10 +6357,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>150</x:v>
@@ -6386,10 +6386,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>659</x:v>
+        <x:v>658.5</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-11.5</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>150</x:v>
@@ -6415,10 +6415,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>150</x:v>
@@ -6444,10 +6444,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>150</x:v>
@@ -6473,10 +6473,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>49.62</x:v>
+        <x:v>48.96</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>151</x:v>
@@ -6502,10 +6502,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>152</x:v>
@@ -6531,10 +6531,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>152</x:v>
@@ -6560,10 +6560,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>152</x:v>
@@ -6589,10 +6589,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>153</x:v>
@@ -6618,10 +6618,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>154</x:v>
@@ -6647,10 +6647,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>154</x:v>
@@ -6676,10 +6676,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>155</x:v>
@@ -6705,10 +6705,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>156</x:v>
@@ -6734,10 +6734,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>156</x:v>
@@ -6763,10 +6763,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>157</x:v>
@@ -6792,10 +6792,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>158</x:v>
@@ -6821,10 +6821,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>158</x:v>
@@ -6850,10 +6850,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>159</x:v>
@@ -6879,10 +6879,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B199" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>159</x:v>
@@ -6908,10 +6908,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>160</x:v>
@@ -6937,10 +6937,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>20.16</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>160</x:v>
@@ -6966,10 +6966,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>160</x:v>
@@ -6995,10 +6995,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>24.04</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>162</x:v>
@@ -7024,10 +7024,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>162</x:v>
@@ -7053,10 +7053,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>162</x:v>
@@ -7082,10 +7082,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>162</x:v>
@@ -7111,10 +7111,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>162</x:v>
@@ -7140,10 +7140,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B208" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>162</x:v>
@@ -7169,10 +7169,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>24.04</x:v>
+        <x:v>22.96</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-1.08</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>164</x:v>
@@ -7198,10 +7198,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>164</x:v>
@@ -7227,10 +7227,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>164</x:v>
@@ -7256,10 +7256,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>165</x:v>
@@ -7285,10 +7285,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>166</x:v>
@@ -7314,10 +7314,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>166</x:v>
@@ -7343,10 +7343,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>166</x:v>
@@ -7372,10 +7372,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>167</x:v>
@@ -7401,10 +7401,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>167</x:v>
@@ -7430,10 +7430,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>167</x:v>
@@ -7459,10 +7459,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>168</x:v>
@@ -7488,10 +7488,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>168</x:v>
@@ -7517,10 +7517,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>169</x:v>
@@ -7546,10 +7546,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>169</x:v>
@@ -7575,10 +7575,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B223" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>169</x:v>
@@ -7604,10 +7604,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>659</x:v>
+        <x:v>658.5</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>-11.5</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>170</x:v>
@@ -7633,10 +7633,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>170</x:v>
@@ -7662,10 +7662,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>170</x:v>
@@ -7691,10 +7691,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>170</x:v>
@@ -7720,10 +7720,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>171</x:v>
@@ -7749,10 +7749,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B229" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>171</x:v>
@@ -7778,10 +7778,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>171</x:v>
@@ -7807,10 +7807,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>171</x:v>
@@ -7836,10 +7836,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>172</x:v>
@@ -7865,10 +7865,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>28.78</x:v>
+        <x:v>29.04</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>0.38</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>172</x:v>
@@ -7894,10 +7894,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>174</x:v>
@@ -7923,10 +7923,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>175</x:v>
@@ -7952,10 +7952,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>176</x:v>
@@ -7981,10 +7981,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>106.1</x:v>
+        <x:v>95.5</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>4</x:v>
+        <x:v>-10.6</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>176</x:v>
@@ -8010,10 +8010,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B238" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>176</x:v>
@@ -8039,10 +8039,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>3.08</x:v>
+        <x:v>3.02</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>0.03</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>176</x:v>
@@ -8068,10 +8068,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>176</x:v>
@@ -8097,10 +8097,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>176</x:v>
@@ -8126,10 +8126,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>178</x:v>
@@ -8155,10 +8155,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>178</x:v>
@@ -8184,10 +8184,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>178</x:v>
@@ -8213,10 +8213,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>11.74</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>180</x:v>
@@ -8242,10 +8242,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>11.74</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>180</x:v>
@@ -8271,10 +8271,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>11.74</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>0.25</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>180</x:v>
@@ -8300,10 +8300,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>180</x:v>
@@ -8329,10 +8329,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>182</x:v>
@@ -8358,10 +8358,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>182</x:v>
@@ -8387,10 +8387,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>183</x:v>
@@ -8416,10 +8416,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B252" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>184</x:v>
@@ -8445,10 +8445,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>184</x:v>
@@ -8474,10 +8474,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>3.35</x:v>
+        <x:v>3.29</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>184</x:v>
@@ -8503,10 +8503,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>184</x:v>
@@ -8532,10 +8532,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>184</x:v>
@@ -8561,10 +8561,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>151.5</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>13.7</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>186</x:v>
@@ -8590,10 +8590,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>186</x:v>
@@ -8619,10 +8619,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>187</x:v>
@@ -8648,10 +8648,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>187</x:v>
@@ -8677,10 +8677,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>187</x:v>
@@ -8706,10 +8706,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>188</x:v>
@@ -8735,10 +8735,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>188</x:v>
@@ -8764,10 +8764,10 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>34.26</x:v>
+        <x:v>32.88</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>0.88</x:v>
+        <x:v>-1.38</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>188</x:v>
@@ -8793,10 +8793,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>16.62</x:v>
+        <x:v>16.14</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>0.27</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>188</x:v>
@@ -8822,10 +8822,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>191</x:v>
@@ -8851,10 +8851,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>191</x:v>
@@ -8880,10 +8880,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>192</x:v>
@@ -8909,10 +8909,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>83</x:v>
+        <x:v>82.05</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>0.8</x:v>
+        <x:v>-0.95</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>194</x:v>
@@ -8938,10 +8938,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>194</x:v>
@@ -8967,10 +8967,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B271" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>195</x:v>
@@ -8996,10 +8996,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B272" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>195</x:v>
@@ -9025,10 +9025,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>195</x:v>
@@ -9054,10 +9054,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-0.57</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>195</x:v>
@@ -9083,10 +9083,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>195</x:v>
@@ -9112,10 +9112,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>195</x:v>
@@ -9141,10 +9141,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>195</x:v>
@@ -9170,10 +9170,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>195</x:v>
@@ -9199,10 +9199,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>196</x:v>
@@ -9228,10 +9228,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>196</x:v>
@@ -9257,10 +9257,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>28.78</x:v>
+        <x:v>29.04</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>0.38</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>196</x:v>
@@ -9286,10 +9286,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>196</x:v>
@@ -9315,10 +9315,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>197</x:v>
@@ -9344,10 +9344,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B284" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>197</x:v>
@@ -9373,10 +9373,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>197</x:v>
@@ -9402,10 +9402,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>7.23</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>0.19</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>199</x:v>
@@ -9431,10 +9431,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B287" s="0">
-        <x:v>30.26</x:v>
+        <x:v>30.2</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>0.84</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>200</x:v>
@@ -9460,10 +9460,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>200</x:v>
@@ -9489,10 +9489,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>200</x:v>
@@ -9518,10 +9518,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>201</x:v>
@@ -9547,10 +9547,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>14.03</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>201</x:v>
@@ -9576,10 +9576,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>202</x:v>
@@ -9605,10 +9605,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>203</x:v>
@@ -9634,10 +9634,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>203</x:v>
@@ -9663,10 +9663,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>203</x:v>
@@ -9692,10 +9692,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>15.57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>-0.04</x:v>
+        <x:v>-0.57</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>204</x:v>
@@ -9721,10 +9721,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>205</x:v>
@@ -9750,10 +9750,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B298" s="0">
-        <x:v>12.1</x:v>
+        <x:v>11.28</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>0.55</x:v>
+        <x:v>-0.82</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>206</x:v>
@@ -9779,10 +9779,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>207</x:v>
@@ -9808,10 +9808,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>207</x:v>
@@ -9837,10 +9837,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>208</x:v>
@@ -9866,10 +9866,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B302" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>209</x:v>
@@ -9895,10 +9895,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>209</x:v>
@@ -9924,10 +9924,10 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>20.16</x:v>
+        <x:v>19.2</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>0.36</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>210</x:v>
@@ -9953,10 +9953,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>210</x:v>
@@ -9982,10 +9982,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B306" s="0">
-        <x:v>9.59</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>0.42</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>211</x:v>
@@ -10011,10 +10011,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>4.19</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>0.03</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>212</x:v>
@@ -10040,10 +10040,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>212</x:v>
@@ -10069,10 +10069,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>212</x:v>
@@ -10098,10 +10098,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>212</x:v>
@@ -10127,10 +10127,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>213</x:v>
@@ -10156,10 +10156,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>213</x:v>
@@ -10185,10 +10185,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>13.9</x:v>
+        <x:v>13.19</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>0.99</x:v>
+        <x:v>-0.71</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>213</x:v>
@@ -10214,10 +10214,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C314" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
         <x:v>215</x:v>
@@ -10243,10 +10243,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>216</x:v>
@@ -10272,10 +10272,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>217</x:v>
@@ -10301,10 +10301,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>217</x:v>
@@ -10330,10 +10330,10 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>49.62</x:v>
+        <x:v>48.96</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>-0.36</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>217</x:v>
@@ -10359,10 +10359,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>218</x:v>
@@ -10388,10 +10388,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>1.99</x:v>
+        <x:v>1.97</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>0.05</x:v>
+        <x:v>-0.02</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>218</x:v>
@@ -10417,10 +10417,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>218</x:v>
@@ -10446,10 +10446,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>218</x:v>
@@ -10475,10 +10475,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>220</x:v>
@@ -10504,10 +10504,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>221</x:v>
@@ -10533,10 +10533,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>221</x:v>
@@ -10562,10 +10562,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>222</x:v>
@@ -10591,10 +10591,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>53.7</x:v>
+        <x:v>52.3</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>0.4</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>223</x:v>
@@ -10620,10 +10620,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>223</x:v>
@@ -10649,10 +10649,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>123.3</x:v>
+        <x:v>123.9</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>-0.5</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>223</x:v>
@@ -10678,10 +10678,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>2.09</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>0.06</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>225</x:v>
@@ -10707,10 +10707,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>19.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>0.97</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>225</x:v>
@@ -10736,10 +10736,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>15.81</x:v>
+        <x:v>15.17</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>0.41</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>226</x:v>
@@ -10765,10 +10765,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>227</x:v>
@@ -10794,10 +10794,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>228</x:v>
@@ -10823,10 +10823,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>228</x:v>
@@ -10852,10 +10852,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B336" s="0">
-        <x:v>23.8</x:v>
+        <x:v>22.9</x:v>
       </x:c>
       <x:c r="C336" s="0">
-        <x:v>0.74</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
         <x:v>229</x:v>
@@ -10881,10 +10881,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B337" s="0">
-        <x:v>27.96</x:v>
+        <x:v>27.1</x:v>
       </x:c>
       <x:c r="C337" s="0">
-        <x:v>0.34</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
         <x:v>229</x:v>
@@ -10910,10 +10910,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B338" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C338" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
         <x:v>230</x:v>
@@ -10939,10 +10939,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B339" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C339" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
         <x:v>230</x:v>
@@ -10968,10 +10968,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B340" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="C340" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
         <x:v>230</x:v>
@@ -10997,10 +10997,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B341" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C341" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
         <x:v>230</x:v>
@@ -11026,10 +11026,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B342" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C342" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
         <x:v>230</x:v>
@@ -11055,10 +11055,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B343" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C343" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
         <x:v>230</x:v>
@@ -11084,10 +11084,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B344" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C344" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
         <x:v>231</x:v>
@@ -11113,10 +11113,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B345" s="0">
-        <x:v>15.36</x:v>
+        <x:v>14.76</x:v>
       </x:c>
       <x:c r="C345" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.6</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
         <x:v>232</x:v>
@@ -11142,10 +11142,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B346" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C346" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
         <x:v>232</x:v>
@@ -11171,10 +11171,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B347" s="0">
-        <x:v>20.9</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C347" s="0">
-        <x:v>0.78</x:v>
+        <x:v>-1.47</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
         <x:v>233</x:v>
@@ -11200,10 +11200,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B348" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="C348" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
         <x:v>233</x:v>
@@ -11229,10 +11229,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B349" s="0">
-        <x:v>19.07</x:v>
+        <x:v>18.32</x:v>
       </x:c>
       <x:c r="C349" s="0">
-        <x:v>-0.22</x:v>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
         <x:v>233</x:v>
@@ -11258,10 +11258,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B350" s="0">
-        <x:v>351.25</x:v>
+        <x:v>341.75</x:v>
       </x:c>
       <x:c r="C350" s="0">
-        <x:v>2.5</x:v>
+        <x:v>-9.5</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
         <x:v>234</x:v>
@@ -11287,10 +11287,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B351" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C351" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
         <x:v>234</x:v>
@@ -11316,10 +11316,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B352" s="0">
-        <x:v>8.88</x:v>
+        <x:v>8.57</x:v>
       </x:c>
       <x:c r="C352" s="0">
-        <x:v>0.24</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
         <x:v>234</x:v>
@@ -11345,10 +11345,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B353" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C353" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
         <x:v>234</x:v>
@@ -11374,10 +11374,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B354" s="0">
-        <x:v>19.7</x:v>
+        <x:v>18.7</x:v>
       </x:c>
       <x:c r="C354" s="0">
-        <x:v>0.97</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
         <x:v>234</x:v>
@@ -11403,10 +11403,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B355" s="0">
-        <x:v>9.59</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="C355" s="0">
-        <x:v>0.42</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
         <x:v>235</x:v>
@@ -11432,10 +11432,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B356" s="0">
-        <x:v>9.59</x:v>
+        <x:v>9.26</x:v>
       </x:c>
       <x:c r="C356" s="0">
-        <x:v>0.42</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
         <x:v>235</x:v>
@@ -11461,10 +11461,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B357" s="0">
-        <x:v>16.28</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="C357" s="0">
-        <x:v>1.48</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
         <x:v>235</x:v>
@@ -11490,10 +11490,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B358" s="0">
-        <x:v>3.64</x:v>
+        <x:v>3.45</x:v>
       </x:c>
       <x:c r="C358" s="0">
-        <x:v>-0.02</x:v>
+        <x:v>-0.19</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
         <x:v>235</x:v>
@@ -11519,10 +11519,10 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B359" s="0">
-        <x:v>12.57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C359" s="0">
-        <x:v>0.12</x:v>
+        <x:v>-0.57</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
         <x:v>235</x:v>
@@ -11548,10 +11548,10 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B360" s="0">
-        <x:v>10.5</x:v>
+        <x:v>10.18</x:v>
       </x:c>
       <x:c r="C360" s="0">
-        <x:v>0.38</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D360" s="0" t="s">
         <x:v>239</x:v>
@@ -11577,10 +11577,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B361" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C361" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D361" s="0" t="s">
         <x:v>239</x:v>
@@ -11606,10 +11606,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B362" s="0">
-        <x:v>3.69</x:v>
+        <x:v>3.55</x:v>
       </x:c>
       <x:c r="C362" s="0">
-        <x:v>0.04</x:v>
+        <x:v>-0.14</x:v>
       </x:c>
       <x:c r="D362" s="0" t="s">
         <x:v>239</x:v>
@@ -11635,10 +11635,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B363" s="0">
-        <x:v>9.57</x:v>
+        <x:v>9.67</x:v>
       </x:c>
       <x:c r="C363" s="0">
-        <x:v>0.81</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="D363" s="0" t="s">
         <x:v>240</x:v>
@@ -11664,10 +11664,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B364" s="0">
-        <x:v>29.62</x:v>
+        <x:v>28.76</x:v>
       </x:c>
       <x:c r="C364" s="0">
-        <x:v>0.32</x:v>
+        <x:v>-0.86</x:v>
       </x:c>
       <x:c r="D364" s="0" t="s">
         <x:v>240</x:v>
@@ -11693,10 +11693,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B365" s="0">
-        <x:v>751.5</x:v>
+        <x:v>676.5</x:v>
       </x:c>
       <x:c r="C365" s="0">
-        <x:v>-83</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="D365" s="0" t="s">
         <x:v>240</x:v>
@@ -11722,10 +11722,10 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B366" s="0">
-        <x:v>3.55</x:v>
+        <x:v>3.49</x:v>
       </x:c>
       <x:c r="C366" s="0">
-        <x:v>0.2</x:v>
+        <x:v>-0.06</x:v>
       </x:c>
       <x:c r="D366" s="0" t="s">
         <x:v>242</x:v>
@@ -11751,10 +11751,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B367" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C367" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D367" s="0" t="s">
         <x:v>242</x:v>
@@ -11780,10 +11780,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B368" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C368" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D368" s="0" t="s">
         <x:v>242</x:v>
@@ -11809,10 +11809,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B369" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C369" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D369" s="0" t="s">
         <x:v>242</x:v>
@@ -11838,10 +11838,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B370" s="0">
-        <x:v>16.28</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="C370" s="0">
-        <x:v>1.48</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D370" s="0" t="s">
         <x:v>242</x:v>
@@ -11867,10 +11867,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B371" s="0">
-        <x:v>41.94</x:v>
+        <x:v>40.4</x:v>
       </x:c>
       <x:c r="C371" s="0">
-        <x:v>1.24</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D371" s="0" t="s">
         <x:v>242</x:v>
@@ -11896,10 +11896,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B372" s="0">
-        <x:v>25.72</x:v>
+        <x:v>24.44</x:v>
       </x:c>
       <x:c r="C372" s="0">
-        <x:v>-0.42</x:v>
+        <x:v>-1.28</x:v>
       </x:c>
       <x:c r="D372" s="0" t="s">
         <x:v>244</x:v>
@@ -11925,10 +11925,10 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B373" s="0">
-        <x:v>16.28</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="C373" s="0">
-        <x:v>1.48</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D373" s="0" t="s">
         <x:v>245</x:v>
@@ -11954,10 +11954,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B374" s="0">
-        <x:v>10.4</x:v>
+        <x:v>10.12</x:v>
       </x:c>
       <x:c r="C374" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.28</x:v>
       </x:c>
       <x:c r="D374" s="0" t="s">
         <x:v>246</x:v>
@@ -11983,10 +11983,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B375" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C375" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
         <x:v>246</x:v>
@@ -12012,10 +12012,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B376" s="0">
-        <x:v>13</x:v>
+        <x:v>12.6</x:v>
       </x:c>
       <x:c r="C376" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
         <x:v>247</x:v>
@@ -12041,10 +12041,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B377" s="0">
-        <x:v>23.16</x:v>
+        <x:v>22.8</x:v>
       </x:c>
       <x:c r="C377" s="0">
-        <x:v>0.46</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D377" s="0" t="s">
         <x:v>248</x:v>
@@ -12070,10 +12070,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B378" s="0">
-        <x:v>3.1</x:v>
+        <x:v>3.01</x:v>
       </x:c>
       <x:c r="C378" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D378" s="0" t="s">
         <x:v>250</x:v>
@@ -12099,10 +12099,10 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B379" s="0">
-        <x:v>72.4</x:v>
+        <x:v>69.15</x:v>
       </x:c>
       <x:c r="C379" s="0">
-        <x:v>0.95</x:v>
+        <x:v>-3.25</x:v>
       </x:c>
       <x:c r="D379" s="0" t="s">
         <x:v>251</x:v>
@@ -12128,10 +12128,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B380" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C380" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D380" s="0" t="s">
         <x:v>251</x:v>
@@ -12157,10 +12157,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B381" s="0">
-        <x:v>0.8</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="C381" s="0">
-        <x:v>0.07</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D381" s="0" t="s">
         <x:v>252</x:v>
@@ -12186,10 +12186,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B382" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C382" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D382" s="0" t="s">
         <x:v>253</x:v>
@@ -12215,10 +12215,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B383" s="0">
-        <x:v>89.65</x:v>
+        <x:v>89.7</x:v>
       </x:c>
       <x:c r="C383" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="D383" s="0" t="s">
         <x:v>253</x:v>
@@ -12244,10 +12244,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B384" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C384" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D384" s="0" t="s">
         <x:v>253</x:v>
@@ -12273,10 +12273,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B385" s="0">
-        <x:v>5.03</x:v>
+        <x:v>4.81</x:v>
       </x:c>
       <x:c r="C385" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D385" s="0" t="s">
         <x:v>253</x:v>
@@ -12302,10 +12302,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B386" s="0">
-        <x:v>204.4</x:v>
+        <x:v>197.5</x:v>
       </x:c>
       <x:c r="C386" s="0">
-        <x:v>6.9</x:v>
+        <x:v>-6.9</x:v>
       </x:c>
       <x:c r="D386" s="0" t="s">
         <x:v>254</x:v>
@@ -12331,10 +12331,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B387" s="0">
-        <x:v>67.1</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="C387" s="0">
-        <x:v>2.45</x:v>
+        <x:v>-0.8</x:v>
       </x:c>
       <x:c r="D387" s="0" t="s">
         <x:v>254</x:v>
@@ -12360,10 +12360,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B388" s="0">
-        <x:v>95.6</x:v>
+        <x:v>96.1</x:v>
       </x:c>
       <x:c r="C388" s="0">
-        <x:v>-10.6</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D388" s="0" t="s">
         <x:v>254</x:v>

--- a/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
+++ b/app/borsa/yeni-is-anlasmalari/data/yeni-is-anlasmalari.xlsx
@@ -1184,10 +1184,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>17.67</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>7.07</x:v>
+        <x:v>7.09</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>0.02</x:v>
@@ -1242,10 +1242,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>33.56</x:v>
+        <x:v>32.02</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>15</x:v>
@@ -1271,10 +1271,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>18</x:v>
@@ -1300,10 +1300,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>50.05</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>-2.25</x:v>
+        <x:v>-3.05</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>18</x:v>
@@ -1329,10 +1329,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>18</x:v>
@@ -1358,10 +1358,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>23</x:v>
@@ -1387,10 +1387,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>25</x:v>
@@ -1416,10 +1416,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>25</x:v>
@@ -1445,10 +1445,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>27</x:v>
@@ -1474,10 +1474,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>13.89</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>-0.59</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>27</x:v>
@@ -1503,10 +1503,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>9.61</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>-0.73</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>27</x:v>
@@ -1532,10 +1532,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>30</x:v>
@@ -1561,10 +1561,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>30</x:v>
@@ -1590,10 +1590,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
         <x:v>31</x:v>
@@ -1619,10 +1619,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>19.91</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>-1.13</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
         <x:v>31</x:v>
@@ -1648,10 +1648,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
         <x:v>31</x:v>
@@ -1677,10 +1677,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>27.5</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-2.74</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>31</x:v>
@@ -1706,10 +1706,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
         <x:v>31</x:v>
@@ -1735,10 +1735,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>31</x:v>
@@ -1764,10 +1764,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>64.3</x:v>
+        <x:v>62.55</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.75</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
         <x:v>31</x:v>
@@ -1793,10 +1793,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
         <x:v>38</x:v>
@@ -1822,10 +1822,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
         <x:v>38</x:v>
@@ -1851,10 +1851,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
         <x:v>38</x:v>
@@ -1880,10 +1880,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>12.5</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>-0.49</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
         <x:v>38</x:v>
@@ -1909,10 +1909,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
         <x:v>42</x:v>
@@ -1938,10 +1938,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>5.46</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
         <x:v>42</x:v>
@@ -1967,10 +1967,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>42</x:v>
@@ -1996,10 +1996,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
         <x:v>42</x:v>
@@ -2025,10 +2025,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>17.67</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>42</x:v>
@@ -2054,10 +2054,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1.6</x:v>
+        <x:v>1.48</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.12</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>42</x:v>
@@ -2083,10 +2083,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
         <x:v>48</x:v>
@@ -2112,10 +2112,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
         <x:v>48</x:v>
@@ -2141,10 +2141,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>5.46</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
         <x:v>49</x:v>
@@ -2170,10 +2170,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
         <x:v>49</x:v>
@@ -2199,10 +2199,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
         <x:v>51</x:v>
@@ -2228,10 +2228,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
         <x:v>53</x:v>
@@ -2257,10 +2257,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
         <x:v>53</x:v>
@@ -2286,10 +2286,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
         <x:v>53</x:v>
@@ -2315,10 +2315,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
         <x:v>54</x:v>
@@ -2344,10 +2344,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
         <x:v>54</x:v>
@@ -2373,10 +2373,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
         <x:v>54</x:v>
@@ -2402,10 +2402,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
         <x:v>54</x:v>
@@ -2431,10 +2431,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
         <x:v>54</x:v>
@@ -2460,10 +2460,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
         <x:v>57</x:v>
@@ -2489,10 +2489,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
         <x:v>59</x:v>
@@ -2518,10 +2518,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
         <x:v>60</x:v>
@@ -2547,10 +2547,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
         <x:v>60</x:v>
@@ -2576,10 +2576,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>7.63</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.43</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
         <x:v>63</x:v>
@@ -2605,10 +2605,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
         <x:v>63</x:v>
@@ -2634,10 +2634,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
         <x:v>63</x:v>
@@ -2663,10 +2663,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>34.3</x:v>
+        <x:v>31.98</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>-2.02</x:v>
+        <x:v>-2.32</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
         <x:v>63</x:v>
@@ -2692,10 +2692,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
         <x:v>65</x:v>
@@ -2721,10 +2721,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>65</x:v>
@@ -2750,10 +2750,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B56" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C56" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>66</x:v>
@@ -2779,10 +2779,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B57" s="0">
-        <x:v>9.16</x:v>
+        <x:v>8.85</x:v>
       </x:c>
       <x:c r="C57" s="0">
-        <x:v>-0.38</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>66</x:v>
@@ -2808,10 +2808,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B58" s="0">
-        <x:v>9.61</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="C58" s="0">
-        <x:v>-0.73</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>66</x:v>
@@ -2837,10 +2837,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B59" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C59" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>66</x:v>
@@ -2866,10 +2866,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C60" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>66</x:v>
@@ -2895,10 +2895,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B61" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C61" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>66</x:v>
@@ -2924,10 +2924,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B62" s="0">
-        <x:v>50.05</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C62" s="0">
-        <x:v>-2.25</x:v>
+        <x:v>-3.05</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>68</x:v>
@@ -2953,10 +2953,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B63" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.86</x:v>
       </x:c>
       <x:c r="C63" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>70</x:v>
@@ -2982,10 +2982,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B64" s="0">
-        <x:v>7.97</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="C64" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>72</x:v>
@@ -3011,10 +3011,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B65" s="0">
-        <x:v>33.56</x:v>
+        <x:v>32.02</x:v>
       </x:c>
       <x:c r="C65" s="0">
-        <x:v>-0.64</x:v>
+        <x:v>-1.54</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>73</x:v>
@@ -3040,10 +3040,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B66" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C66" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>75</x:v>
@@ -3069,10 +3069,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B67" s="0">
-        <x:v>46</x:v>
+        <x:v>42.26</x:v>
       </x:c>
       <x:c r="C67" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-3.74</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>75</x:v>
@@ -3098,10 +3098,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B68" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C68" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>77</x:v>
@@ -3127,10 +3127,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B69" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C69" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>78</x:v>
@@ -3156,10 +3156,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B70" s="0">
-        <x:v>52.65</x:v>
+        <x:v>49.9</x:v>
       </x:c>
       <x:c r="C70" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-2.75</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>78</x:v>
@@ -3185,10 +3185,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C71" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>78</x:v>
@@ -3214,10 +3214,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B72" s="0">
-        <x:v>20.26</x:v>
+        <x:v>19.52</x:v>
       </x:c>
       <x:c r="C72" s="0">
-        <x:v>-0.2</x:v>
+        <x:v>-0.74</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>78</x:v>
@@ -3243,10 +3243,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B73" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C73" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>78</x:v>
@@ -3272,10 +3272,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B74" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C74" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>83</x:v>
@@ -3301,10 +3301,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B75" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C75" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>84</x:v>
@@ -3330,10 +3330,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B76" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C76" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>84</x:v>
@@ -3359,10 +3359,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B77" s="0">
-        <x:v>69.3</x:v>
+        <x:v>76.2</x:v>
       </x:c>
       <x:c r="C77" s="0">
-        <x:v>-7.7</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>86</x:v>
@@ -3388,10 +3388,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B78" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C78" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>87</x:v>
@@ -3417,10 +3417,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B79" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C79" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>87</x:v>
@@ -3446,10 +3446,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B80" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C80" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>87</x:v>
@@ -3475,10 +3475,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B81" s="0">
-        <x:v>19.91</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C81" s="0">
-        <x:v>-1.13</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>88</x:v>
@@ -3504,10 +3504,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B82" s="0">
-        <x:v>34.3</x:v>
+        <x:v>31.98</x:v>
       </x:c>
       <x:c r="C82" s="0">
-        <x:v>-2.02</x:v>
+        <x:v>-2.32</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>88</x:v>
@@ -3533,10 +3533,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B83" s="0">
-        <x:v>84.85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C83" s="0">
-        <x:v>-4</x:v>
+        <x:v>-0.85</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>90</x:v>
@@ -3562,10 +3562,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B84" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C84" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>90</x:v>
@@ -3591,10 +3591,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B85" s="0">
-        <x:v>662.5</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C85" s="0">
-        <x:v>2</x:v>
+        <x:v>-20.5</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>92</x:v>
@@ -3620,10 +3620,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B86" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C86" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>94</x:v>
@@ -3649,10 +3649,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B87" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C87" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>94</x:v>
@@ -3678,10 +3678,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B88" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C88" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>95</x:v>
@@ -3707,10 +3707,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B89" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C89" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>95</x:v>
@@ -3736,10 +3736,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B90" s="0">
-        <x:v>9.61</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="C90" s="0">
-        <x:v>-0.73</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>96</x:v>
@@ -3765,10 +3765,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B91" s="0">
-        <x:v>17.67</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C91" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>96</x:v>
@@ -3794,10 +3794,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B92" s="0">
-        <x:v>34.3</x:v>
+        <x:v>31.98</x:v>
       </x:c>
       <x:c r="C92" s="0">
-        <x:v>-2.02</x:v>
+        <x:v>-2.32</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>96</x:v>
@@ -3823,10 +3823,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B93" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C93" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>97</x:v>
@@ -3852,10 +3852,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B94" s="0">
-        <x:v>69.3</x:v>
+        <x:v>76.2</x:v>
       </x:c>
       <x:c r="C94" s="0">
-        <x:v>-7.7</x:v>
+        <x:v>6.9</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>97</x:v>
@@ -3881,10 +3881,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="0">
-        <x:v>662.5</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C95" s="0">
-        <x:v>2</x:v>
+        <x:v>-20.5</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>98</x:v>
@@ -3910,10 +3910,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B96" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C96" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>98</x:v>
@@ -3939,10 +3939,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B97" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C97" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>98</x:v>
@@ -3968,10 +3968,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B98" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C98" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>98</x:v>
@@ -3997,10 +3997,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B99" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C99" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>100</x:v>
@@ -4026,10 +4026,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B100" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.86</x:v>
       </x:c>
       <x:c r="C100" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>101</x:v>
@@ -4055,10 +4055,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B101" s="0">
-        <x:v>12.08</x:v>
+        <x:v>11.86</x:v>
       </x:c>
       <x:c r="C101" s="0">
-        <x:v>0.18</x:v>
+        <x:v>-0.22</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>103</x:v>
@@ -4084,10 +4084,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B102" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C102" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>103</x:v>
@@ -4113,10 +4113,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B103" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C103" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>104</x:v>
@@ -4142,10 +4142,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B104" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C104" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>104</x:v>
@@ -4171,10 +4171,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B105" s="0">
-        <x:v>14.18</x:v>
+        <x:v>13.42</x:v>
       </x:c>
       <x:c r="C105" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>106</x:v>
@@ -4200,10 +4200,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B106" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C106" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>107</x:v>
@@ -4229,10 +4229,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B107" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C107" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>107</x:v>
@@ -4258,10 +4258,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B108" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C108" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>107</x:v>
@@ -4287,10 +4287,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B109" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C109" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>108</x:v>
@@ -4316,10 +4316,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B110" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C110" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>108</x:v>
@@ -4345,10 +4345,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B111" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C111" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>109</x:v>
@@ -4374,10 +4374,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B112" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C112" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>109</x:v>
@@ -4403,10 +4403,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0">
-        <x:v>2.45</x:v>
+        <x:v>2.28</x:v>
       </x:c>
       <x:c r="C113" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.17</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>111</x:v>
@@ -4432,10 +4432,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B114" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C114" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>112</x:v>
@@ -4461,10 +4461,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B115" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C115" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>112</x:v>
@@ -4490,10 +4490,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B116" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C116" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>112</x:v>
@@ -4519,10 +4519,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B117" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C117" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>112</x:v>
@@ -4548,10 +4548,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B118" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C118" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>113</x:v>
@@ -4577,10 +4577,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B119" s="0">
-        <x:v>34.3</x:v>
+        <x:v>31.98</x:v>
       </x:c>
       <x:c r="C119" s="0">
-        <x:v>-2.02</x:v>
+        <x:v>-2.32</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>113</x:v>
@@ -4606,10 +4606,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B120" s="0">
-        <x:v>19.76</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C120" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>115</x:v>
@@ -4635,10 +4635,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B121" s="0">
-        <x:v>7.63</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="C121" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.43</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>115</x:v>
@@ -4664,10 +4664,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B122" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C122" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>115</x:v>
@@ -4693,10 +4693,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B123" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C123" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>116</x:v>
@@ -4722,10 +4722,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B124" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.86</x:v>
       </x:c>
       <x:c r="C124" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>117</x:v>
@@ -4751,10 +4751,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B125" s="0">
-        <x:v>7.63</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="C125" s="0">
-        <x:v>-0.09</x:v>
+        <x:v>-0.43</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>117</x:v>
@@ -4780,10 +4780,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B126" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C126" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>117</x:v>
@@ -4809,10 +4809,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B127" s="0">
-        <x:v>57.15</x:v>
+        <x:v>54.95</x:v>
       </x:c>
       <x:c r="C127" s="0">
-        <x:v>-1.4</x:v>
+        <x:v>-2.2</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>119</x:v>
@@ -4838,10 +4838,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B128" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C128" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>119</x:v>
@@ -4867,10 +4867,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B129" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C129" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>119</x:v>
@@ -4896,10 +4896,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B130" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C130" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>121</x:v>
@@ -4925,10 +4925,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B131" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C131" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>121</x:v>
@@ -4954,10 +4954,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B132" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C132" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>122</x:v>
@@ -4983,10 +4983,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B133" s="0">
-        <x:v>9.61</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="C133" s="0">
-        <x:v>-0.73</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>122</x:v>
@@ -5012,10 +5012,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B134" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C134" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>122</x:v>
@@ -5041,10 +5041,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B135" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C135" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>123</x:v>
@@ -5070,10 +5070,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B136" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C136" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>123</x:v>
@@ -5099,10 +5099,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B137" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C137" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>123</x:v>
@@ -5128,10 +5128,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B138" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C138" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>123</x:v>
@@ -5157,10 +5157,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B139" s="0">
-        <x:v>13.22</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C139" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>123</x:v>
@@ -5186,10 +5186,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B140" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C140" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>125</x:v>
@@ -5215,10 +5215,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B141" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C141" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>125</x:v>
@@ -5244,10 +5244,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B142" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C142" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>125</x:v>
@@ -5273,10 +5273,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B143" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C143" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>126</x:v>
@@ -5302,10 +5302,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B144" s="0">
-        <x:v>8.75</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="C144" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>126</x:v>
@@ -5331,10 +5331,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B145" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C145" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>126</x:v>
@@ -5360,10 +5360,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B146" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C146" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>128</x:v>
@@ -5389,10 +5389,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B147" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C147" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>128</x:v>
@@ -5418,10 +5418,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B148" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C148" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>128</x:v>
@@ -5447,10 +5447,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B149" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C149" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>128</x:v>
@@ -5476,10 +5476,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B150" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C150" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>128</x:v>
@@ -5505,10 +5505,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B151" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C151" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>129</x:v>
@@ -5534,10 +5534,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B152" s="0">
-        <x:v>114</x:v>
+        <x:v>102.6</x:v>
       </x:c>
       <x:c r="C152" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-11.4</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>129</x:v>
@@ -5563,10 +5563,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B153" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C153" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>131</x:v>
@@ -5592,10 +5592,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B154" s="0">
-        <x:v>5.28</x:v>
+        <x:v>4.78</x:v>
       </x:c>
       <x:c r="C154" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.5</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>131</x:v>
@@ -5621,10 +5621,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B155" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C155" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>133</x:v>
@@ -5650,10 +5650,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B156" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C156" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>134</x:v>
@@ -5679,10 +5679,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B157" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C157" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>134</x:v>
@@ -5708,10 +5708,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B158" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C158" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>134</x:v>
@@ -5737,10 +5737,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B159" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C159" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>135</x:v>
@@ -5766,10 +5766,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B160" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C160" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>136</x:v>
@@ -5795,10 +5795,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B161" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C161" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>137</x:v>
@@ -5824,10 +5824,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B162" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="C162" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>137</x:v>
@@ -5853,10 +5853,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B163" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C163" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>139</x:v>
@@ -5882,10 +5882,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B164" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C164" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>139</x:v>
@@ -5911,10 +5911,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B165" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C165" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>140</x:v>
@@ -5940,10 +5940,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B166" s="0">
-        <x:v>14.18</x:v>
+        <x:v>13.42</x:v>
       </x:c>
       <x:c r="C166" s="0">
-        <x:v>-0.35</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>141</x:v>
@@ -5969,10 +5969,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B167" s="0">
-        <x:v>13.26</x:v>
+        <x:v>12.72</x:v>
       </x:c>
       <x:c r="C167" s="0">
-        <x:v>-0.44</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>141</x:v>
@@ -5998,10 +5998,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B168" s="0">
-        <x:v>7.97</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="C168" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>143</x:v>
@@ -6027,10 +6027,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B169" s="0">
-        <x:v>27.5</x:v>
+        <x:v>24.76</x:v>
       </x:c>
       <x:c r="C169" s="0">
-        <x:v>0.68</x:v>
+        <x:v>-2.74</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>143</x:v>
@@ -6056,10 +6056,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B170" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C170" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>143</x:v>
@@ -6085,10 +6085,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B171" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C171" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>145</x:v>
@@ -6114,10 +6114,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B172" s="0">
-        <x:v>7.97</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="C172" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>145</x:v>
@@ -6143,10 +6143,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B173" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C173" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>146</x:v>
@@ -6172,10 +6172,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B174" s="0">
-        <x:v>46</x:v>
+        <x:v>42.26</x:v>
       </x:c>
       <x:c r="C174" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-3.74</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>146</x:v>
@@ -6201,10 +6201,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B175" s="0">
-        <x:v>19.91</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C175" s="0">
-        <x:v>-1.13</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>147</x:v>
@@ -6230,10 +6230,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B176" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C176" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>147</x:v>
@@ -6259,10 +6259,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B177" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C177" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>148</x:v>
@@ -6288,10 +6288,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B178" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C178" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>149</x:v>
@@ -6317,10 +6317,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B179" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C179" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>149</x:v>
@@ -6346,10 +6346,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B180" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C180" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>149</x:v>
@@ -6375,10 +6375,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B181" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C181" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>149</x:v>
@@ -6404,10 +6404,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B182" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C182" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>150</x:v>
@@ -6433,10 +6433,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B183" s="0">
-        <x:v>27.04</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C183" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>152</x:v>
@@ -6462,10 +6462,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B184" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C184" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>153</x:v>
@@ -6491,10 +6491,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B185" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C185" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>154</x:v>
@@ -6520,10 +6520,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B186" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C186" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>154</x:v>
@@ -6549,10 +6549,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B187" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C187" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>155</x:v>
@@ -6578,10 +6578,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B188" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C188" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>156</x:v>
@@ -6607,10 +6607,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B189" s="0">
-        <x:v>662.5</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C189" s="0">
-        <x:v>2</x:v>
+        <x:v>-20.5</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>156</x:v>
@@ -6636,10 +6636,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B190" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C190" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>156</x:v>
@@ -6665,10 +6665,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B191" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C191" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>156</x:v>
@@ -6694,10 +6694,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B192" s="0">
-        <x:v>46</x:v>
+        <x:v>42.26</x:v>
       </x:c>
       <x:c r="C192" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-3.74</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>157</x:v>
@@ -6723,10 +6723,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B193" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C193" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>158</x:v>
@@ -6752,10 +6752,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B194" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C194" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>158</x:v>
@@ -6781,10 +6781,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B195" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C195" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>158</x:v>
@@ -6810,10 +6810,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B196" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C196" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>159</x:v>
@@ -6839,10 +6839,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B197" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C197" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>160</x:v>
@@ -6868,10 +6868,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B198" s="0">
-        <x:v>114</x:v>
+        <x:v>102.6</x:v>
       </x:c>
       <x:c r="C198" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-11.4</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>160</x:v>
@@ -6897,10 +6897,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B199" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C199" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>161</x:v>
@@ -6926,10 +6926,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B200" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C200" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>162</x:v>
@@ -6955,10 +6955,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B201" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C201" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>162</x:v>
@@ -6984,10 +6984,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B202" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C202" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>163</x:v>
@@ -7013,10 +7013,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B203" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C203" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>164</x:v>
@@ -7042,10 +7042,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B204" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C204" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>164</x:v>
@@ -7071,10 +7071,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B205" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C205" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>165</x:v>
@@ -7100,10 +7100,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B206" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C206" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>165</x:v>
@@ -7129,10 +7129,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B207" s="0">
-        <x:v>27.04</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C207" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>166</x:v>
@@ -7158,10 +7158,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B208" s="0">
-        <x:v>18.03</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C208" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>166</x:v>
@@ -7187,10 +7187,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B209" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C209" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>166</x:v>
@@ -7216,10 +7216,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B210" s="0">
-        <x:v>19.91</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C210" s="0">
-        <x:v>-1.13</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>168</x:v>
@@ -7245,10 +7245,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B211" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C211" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>168</x:v>
@@ -7274,10 +7274,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B212" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C212" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>168</x:v>
@@ -7303,10 +7303,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B213" s="0">
-        <x:v>2.98</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="C213" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>168</x:v>
@@ -7332,10 +7332,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B214" s="0">
-        <x:v>27.04</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C214" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>168</x:v>
@@ -7361,10 +7361,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B215" s="0">
-        <x:v>114</x:v>
+        <x:v>102.6</x:v>
       </x:c>
       <x:c r="C215" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-11.4</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>168</x:v>
@@ -7390,10 +7390,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B216" s="0">
-        <x:v>19.91</x:v>
+        <x:v>18.9</x:v>
       </x:c>
       <x:c r="C216" s="0">
-        <x:v>-1.13</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>170</x:v>
@@ -7419,10 +7419,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B217" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C217" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>170</x:v>
@@ -7448,10 +7448,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B218" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C218" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>170</x:v>
@@ -7477,10 +7477,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B219" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C219" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>171</x:v>
@@ -7506,10 +7506,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B220" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C220" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>172</x:v>
@@ -7535,10 +7535,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B221" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C221" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>172</x:v>
@@ -7564,10 +7564,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B222" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C222" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>172</x:v>
@@ -7593,10 +7593,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B223" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C223" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>173</x:v>
@@ -7622,10 +7622,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B224" s="0">
-        <x:v>27.04</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C224" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>173</x:v>
@@ -7651,10 +7651,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B225" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C225" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>173</x:v>
@@ -7680,10 +7680,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B226" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C226" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>174</x:v>
@@ -7709,10 +7709,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B227" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C227" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>174</x:v>
@@ -7738,10 +7738,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B228" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C228" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D228" s="0" t="s">
         <x:v>175</x:v>
@@ -7767,10 +7767,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B229" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C229" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D229" s="0" t="s">
         <x:v>175</x:v>
@@ -7796,10 +7796,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B230" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C230" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D230" s="0" t="s">
         <x:v>175</x:v>
@@ -7825,10 +7825,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B231" s="0">
-        <x:v>662.5</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C231" s="0">
-        <x:v>2</x:v>
+        <x:v>-20.5</x:v>
       </x:c>
       <x:c r="D231" s="0" t="s">
         <x:v>176</x:v>
@@ -7854,10 +7854,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B232" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C232" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D232" s="0" t="s">
         <x:v>176</x:v>
@@ -7883,10 +7883,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B233" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C233" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D233" s="0" t="s">
         <x:v>176</x:v>
@@ -7912,10 +7912,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B234" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C234" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D234" s="0" t="s">
         <x:v>176</x:v>
@@ -7941,10 +7941,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B235" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C235" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D235" s="0" t="s">
         <x:v>177</x:v>
@@ -7970,10 +7970,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B236" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C236" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D236" s="0" t="s">
         <x:v>177</x:v>
@@ -7999,10 +7999,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B237" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C237" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D237" s="0" t="s">
         <x:v>177</x:v>
@@ -8028,10 +8028,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B238" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C238" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D238" s="0" t="s">
         <x:v>177</x:v>
@@ -8057,10 +8057,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B239" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C239" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D239" s="0" t="s">
         <x:v>178</x:v>
@@ -8086,10 +8086,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B240" s="0">
-        <x:v>24.42</x:v>
+        <x:v>23.98</x:v>
       </x:c>
       <x:c r="C240" s="0">
-        <x:v>-1.6</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D240" s="0" t="s">
         <x:v>178</x:v>
@@ -8115,10 +8115,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B241" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C241" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D241" s="0" t="s">
         <x:v>180</x:v>
@@ -8144,10 +8144,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B242" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C242" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D242" s="0" t="s">
         <x:v>181</x:v>
@@ -8173,10 +8173,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B243" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C243" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D243" s="0" t="s">
         <x:v>182</x:v>
@@ -8202,10 +8202,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B244" s="0">
-        <x:v>93</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C244" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="D244" s="0" t="s">
         <x:v>182</x:v>
@@ -8231,10 +8231,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B245" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="C245" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D245" s="0" t="s">
         <x:v>182</x:v>
@@ -8260,10 +8260,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B246" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.61</x:v>
       </x:c>
       <x:c r="C246" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D246" s="0" t="s">
         <x:v>182</x:v>
@@ -8289,10 +8289,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B247" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C247" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D247" s="0" t="s">
         <x:v>182</x:v>
@@ -8318,10 +8318,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B248" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C248" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D248" s="0" t="s">
         <x:v>182</x:v>
@@ -8347,10 +8347,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B249" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C249" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D249" s="0" t="s">
         <x:v>184</x:v>
@@ -8376,10 +8376,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B250" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C250" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D250" s="0" t="s">
         <x:v>184</x:v>
@@ -8405,10 +8405,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B251" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C251" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D251" s="0" t="s">
         <x:v>184</x:v>
@@ -8434,10 +8434,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B252" s="0">
-        <x:v>12.02</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="C252" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D252" s="0" t="s">
         <x:v>186</x:v>
@@ -8463,10 +8463,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B253" s="0">
-        <x:v>12.02</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="C253" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D253" s="0" t="s">
         <x:v>186</x:v>
@@ -8492,10 +8492,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B254" s="0">
-        <x:v>12.02</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="C254" s="0">
-        <x:v>0.62</x:v>
+        <x:v>-0.42</x:v>
       </x:c>
       <x:c r="D254" s="0" t="s">
         <x:v>186</x:v>
@@ -8521,10 +8521,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B255" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C255" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D255" s="0" t="s">
         <x:v>186</x:v>
@@ -8550,10 +8550,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B256" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C256" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D256" s="0" t="s">
         <x:v>188</x:v>
@@ -8579,10 +8579,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B257" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C257" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D257" s="0" t="s">
         <x:v>188</x:v>
@@ -8608,10 +8608,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B258" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C258" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D258" s="0" t="s">
         <x:v>189</x:v>
@@ -8637,10 +8637,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B259" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C259" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D259" s="0" t="s">
         <x:v>190</x:v>
@@ -8666,10 +8666,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B260" s="0">
-        <x:v>2.98</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="C260" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D260" s="0" t="s">
         <x:v>190</x:v>
@@ -8695,10 +8695,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B261" s="0">
-        <x:v>2.98</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="C261" s="0">
-        <x:v>-0.07</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="D261" s="0" t="s">
         <x:v>190</x:v>
@@ -8724,10 +8724,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B262" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C262" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D262" s="0" t="s">
         <x:v>190</x:v>
@@ -8753,10 +8753,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B263" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C263" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D263" s="0" t="s">
         <x:v>190</x:v>
@@ -8782,10 +8782,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B264" s="0">
-        <x:v>144</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C264" s="0">
-        <x:v>-9.4</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="D264" s="0" t="s">
         <x:v>192</x:v>
@@ -8811,10 +8811,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B265" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C265" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D265" s="0" t="s">
         <x:v>192</x:v>
@@ -8840,10 +8840,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B266" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C266" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D266" s="0" t="s">
         <x:v>193</x:v>
@@ -8869,10 +8869,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B267" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C267" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D267" s="0" t="s">
         <x:v>193</x:v>
@@ -8898,10 +8898,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B268" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C268" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D268" s="0" t="s">
         <x:v>193</x:v>
@@ -8927,10 +8927,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B269" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C269" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D269" s="0" t="s">
         <x:v>194</x:v>
@@ -8956,10 +8956,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B270" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C270" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D270" s="0" t="s">
         <x:v>194</x:v>
@@ -8985,10 +8985,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="B271" s="0">
-        <x:v>30.52</x:v>
+        <x:v>29.88</x:v>
       </x:c>
       <x:c r="C271" s="0">
-        <x:v>-1.48</x:v>
+        <x:v>-0.64</x:v>
       </x:c>
       <x:c r="D271" s="0" t="s">
         <x:v>194</x:v>
@@ -9014,10 +9014,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B272" s="0">
-        <x:v>14.64</x:v>
+        <x:v>14.24</x:v>
       </x:c>
       <x:c r="C272" s="0">
-        <x:v>-0.67</x:v>
+        <x:v>-0.4</x:v>
       </x:c>
       <x:c r="D272" s="0" t="s">
         <x:v>194</x:v>
@@ -9043,10 +9043,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B273" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C273" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D273" s="0" t="s">
         <x:v>197</x:v>
@@ -9072,10 +9072,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B274" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C274" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D274" s="0" t="s">
         <x:v>197</x:v>
@@ -9101,10 +9101,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B275" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C275" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D275" s="0" t="s">
         <x:v>198</x:v>
@@ -9130,10 +9130,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B276" s="0">
-        <x:v>71.7</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="C276" s="0">
-        <x:v>-3.3</x:v>
+        <x:v>-3.2</x:v>
       </x:c>
       <x:c r="D276" s="0" t="s">
         <x:v>200</x:v>
@@ -9159,10 +9159,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B277" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C277" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D277" s="0" t="s">
         <x:v>200</x:v>
@@ -9188,10 +9188,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B278" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C278" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D278" s="0" t="s">
         <x:v>201</x:v>
@@ -9217,10 +9217,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B279" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C279" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D279" s="0" t="s">
         <x:v>201</x:v>
@@ -9246,10 +9246,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B280" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C280" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D280" s="0" t="s">
         <x:v>201</x:v>
@@ -9275,10 +9275,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B281" s="0">
-        <x:v>13.89</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="C281" s="0">
-        <x:v>-0.59</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D281" s="0" t="s">
         <x:v>201</x:v>
@@ -9304,10 +9304,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B282" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C282" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D282" s="0" t="s">
         <x:v>201</x:v>
@@ -9333,10 +9333,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B283" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C283" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D283" s="0" t="s">
         <x:v>201</x:v>
@@ -9362,10 +9362,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B284" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C284" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D284" s="0" t="s">
         <x:v>201</x:v>
@@ -9391,10 +9391,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B285" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C285" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D285" s="0" t="s">
         <x:v>201</x:v>
@@ -9420,10 +9420,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B286" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C286" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D286" s="0" t="s">
         <x:v>202</x:v>
@@ -9449,10 +9449,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B287" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C287" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D287" s="0" t="s">
         <x:v>202</x:v>
@@ -9478,10 +9478,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B288" s="0">
-        <x:v>24.42</x:v>
+        <x:v>23.98</x:v>
       </x:c>
       <x:c r="C288" s="0">
-        <x:v>-1.6</x:v>
+        <x:v>-0.44</x:v>
       </x:c>
       <x:c r="D288" s="0" t="s">
         <x:v>202</x:v>
@@ -9507,10 +9507,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B289" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C289" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D289" s="0" t="s">
         <x:v>202</x:v>
@@ -9536,10 +9536,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B290" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C290" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D290" s="0" t="s">
         <x:v>203</x:v>
@@ -9565,10 +9565,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B291" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C291" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D291" s="0" t="s">
         <x:v>203</x:v>
@@ -9594,10 +9594,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B292" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C292" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D292" s="0" t="s">
         <x:v>203</x:v>
@@ -9623,10 +9623,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B293" s="0">
-        <x:v>7.03</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="C293" s="0">
-        <x:v>-0.05</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D293" s="0" t="s">
         <x:v>205</x:v>
@@ -9652,10 +9652,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B294" s="0">
-        <x:v>27.04</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C294" s="0">
-        <x:v>-2.92</x:v>
+        <x:v>-0.04</x:v>
       </x:c>
       <x:c r="D294" s="0" t="s">
         <x:v>206</x:v>
@@ -9681,10 +9681,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B295" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C295" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D295" s="0" t="s">
         <x:v>206</x:v>
@@ -9710,10 +9710,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B296" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C296" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D296" s="0" t="s">
         <x:v>206</x:v>
@@ -9739,10 +9739,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B297" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C297" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D297" s="0" t="s">
         <x:v>207</x:v>
@@ -9768,10 +9768,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B298" s="0">
-        <x:v>13.6</x:v>
+        <x:v>13.86</x:v>
       </x:c>
       <x:c r="C298" s="0">
-        <x:v>-0.6</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="D298" s="0" t="s">
         <x:v>207</x:v>
@@ -9797,10 +9797,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B299" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C299" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D299" s="0" t="s">
         <x:v>208</x:v>
@@ -9826,10 +9826,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B300" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C300" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D300" s="0" t="s">
         <x:v>209</x:v>
@@ -9855,10 +9855,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B301" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C301" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D301" s="0" t="s">
         <x:v>209</x:v>
@@ -9884,10 +9884,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B302" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C302" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D302" s="0" t="s">
         <x:v>209</x:v>
@@ -9913,10 +9913,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B303" s="0">
-        <x:v>13.89</x:v>
+        <x:v>15.03</x:v>
       </x:c>
       <x:c r="C303" s="0">
-        <x:v>-0.59</x:v>
+        <x:v>1.14</x:v>
       </x:c>
       <x:c r="D303" s="0" t="s">
         <x:v>210</x:v>
@@ -9942,10 +9942,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B304" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C304" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D304" s="0" t="s">
         <x:v>211</x:v>
@@ -9971,10 +9971,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B305" s="0">
-        <x:v>9.61</x:v>
+        <x:v>9.3</x:v>
       </x:c>
       <x:c r="C305" s="0">
-        <x:v>-0.73</x:v>
+        <x:v>-0.31</x:v>
       </x:c>
       <x:c r="D305" s="0" t="s">
         <x:v>212</x:v>
@@ -10000,10 +10000,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B306" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C306" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D306" s="0" t="s">
         <x:v>213</x:v>
@@ -10029,10 +10029,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B307" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C307" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D307" s="0" t="s">
         <x:v>213</x:v>
@@ -10058,10 +10058,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B308" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C308" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D308" s="0" t="s">
         <x:v>214</x:v>
@@ -10087,10 +10087,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B309" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C309" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D309" s="0" t="s">
         <x:v>215</x:v>
@@ -10116,10 +10116,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B310" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C310" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D310" s="0" t="s">
         <x:v>215</x:v>
@@ -10145,10 +10145,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B311" s="0">
-        <x:v>18.03</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C311" s="0">
-        <x:v>-0.32</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D311" s="0" t="s">
         <x:v>216</x:v>
@@ -10174,10 +10174,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B312" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C312" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D312" s="0" t="s">
         <x:v>216</x:v>
@@ -10203,10 +10203,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B313" s="0">
-        <x:v>8.75</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="C313" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D313" s="0" t="s">
         <x:v>217</x:v>
@@ -10232,10 +10232,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B314" s="0">
-        <x:v>3.92</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C314" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-0.36</x:v>
       </x:c>
       <x:c r="D314" s="0" t="s">
         <x:v>218</x:v>
@@ -10261,10 +10261,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B315" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C315" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D315" s="0" t="s">
         <x:v>218</x:v>
@@ -10290,10 +10290,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B316" s="0">
-        <x:v>13.22</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C316" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D316" s="0" t="s">
         <x:v>218</x:v>
@@ -10319,10 +10319,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B317" s="0">
-        <x:v>13.22</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C317" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D317" s="0" t="s">
         <x:v>218</x:v>
@@ -10348,10 +10348,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B318" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C318" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D318" s="0" t="s">
         <x:v>219</x:v>
@@ -10377,10 +10377,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B319" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C319" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D319" s="0" t="s">
         <x:v>219</x:v>
@@ -10406,10 +10406,10 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B320" s="0">
-        <x:v>12.3</x:v>
+        <x:v>11.6</x:v>
       </x:c>
       <x:c r="C320" s="0">
-        <x:v>-0.49</x:v>
+        <x:v>-0.7</x:v>
       </x:c>
       <x:c r="D320" s="0" t="s">
         <x:v>219</x:v>
@@ -10435,10 +10435,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B321" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C321" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D321" s="0" t="s">
         <x:v>221</x:v>
@@ -10464,10 +10464,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B322" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C322" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D322" s="0" t="s">
         <x:v>222</x:v>
@@ -10493,10 +10493,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B323" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C323" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D323" s="0" t="s">
         <x:v>223</x:v>
@@ -10522,10 +10522,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B324" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C324" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D324" s="0" t="s">
         <x:v>223</x:v>
@@ -10551,10 +10551,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B325" s="0">
-        <x:v>46</x:v>
+        <x:v>42.26</x:v>
       </x:c>
       <x:c r="C325" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-3.74</x:v>
       </x:c>
       <x:c r="D325" s="0" t="s">
         <x:v>223</x:v>
@@ -10580,10 +10580,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B326" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C326" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D326" s="0" t="s">
         <x:v>224</x:v>
@@ -10609,10 +10609,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B327" s="0">
-        <x:v>1.82</x:v>
+        <x:v>1.71</x:v>
       </x:c>
       <x:c r="C327" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.11</x:v>
       </x:c>
       <x:c r="D327" s="0" t="s">
         <x:v>224</x:v>
@@ -10638,10 +10638,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B328" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="C328" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D328" s="0" t="s">
         <x:v>224</x:v>
@@ -10667,10 +10667,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B329" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C329" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D329" s="0" t="s">
         <x:v>224</x:v>
@@ -10696,10 +10696,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B330" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C330" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D330" s="0" t="s">
         <x:v>226</x:v>
@@ -10725,10 +10725,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B331" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C331" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D331" s="0" t="s">
         <x:v>227</x:v>
@@ -10754,10 +10754,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B332" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C332" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D332" s="0" t="s">
         <x:v>227</x:v>
@@ -10783,10 +10783,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B333" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C333" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D333" s="0" t="s">
         <x:v>228</x:v>
@@ -10812,10 +10812,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B334" s="0">
-        <x:v>46.56</x:v>
+        <x:v>44.02</x:v>
       </x:c>
       <x:c r="C334" s="0">
-        <x:v>-3.38</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="D334" s="0" t="s">
         <x:v>229</x:v>
@@ -10841,10 +10841,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B335" s="0">
-        <x:v>114</x:v>
+        <x:v>102.6</x:v>
       </x:c>
       <x:c r="C335" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-11.4</x:v>
       </x:c>
       <x:c r="D335" s="0" t="s">
         <x:v>229</x:v>
@@ -10870,10 +10870,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B336" s="0">
-        <x:v>114</x:v>
+        <x:v>102.6</x:v>
       </x:c>
       <x:c r="C336" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-11.4</x:v>
       </x:c>
       <x:c r="D336" s="0" t="s">
         <x:v>229</x:v>
@@ -10899,10 +10899,10 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B337" s="0">
-        <x:v>1.7</x:v>
+        <x:v>1.62</x:v>
       </x:c>
       <x:c r="C337" s="0">
-        <x:v>-0.17</x:v>
+        <x:v>-0.08</x:v>
       </x:c>
       <x:c r="D337" s="0" t="s">
         <x:v>231</x:v>
@@ -10928,10 +10928,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B338" s="0">
-        <x:v>17.67</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C338" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D338" s="0" t="s">
         <x:v>231</x:v>
@@ -10957,10 +10957,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B339" s="0">
-        <x:v>14.08</x:v>
+        <x:v>13.49</x:v>
       </x:c>
       <x:c r="C339" s="0">
-        <x:v>-0.8</x:v>
+        <x:v>-0.59</x:v>
       </x:c>
       <x:c r="D339" s="0" t="s">
         <x:v>232</x:v>
@@ -10986,10 +10986,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B340" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C340" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D340" s="0" t="s">
         <x:v>233</x:v>
@@ -11015,10 +11015,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B341" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="C341" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D341" s="0" t="s">
         <x:v>234</x:v>
@@ -11044,10 +11044,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B342" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C342" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D342" s="0" t="s">
         <x:v>234</x:v>
@@ -11073,10 +11073,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B343" s="0">
-        <x:v>19.76</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C343" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D343" s="0" t="s">
         <x:v>235</x:v>
@@ -11102,10 +11102,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B344" s="0">
-        <x:v>24.7</x:v>
+        <x:v>24.08</x:v>
       </x:c>
       <x:c r="C344" s="0">
-        <x:v>-1.72</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D344" s="0" t="s">
         <x:v>235</x:v>
@@ -11131,10 +11131,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B345" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C345" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D345" s="0" t="s">
         <x:v>236</x:v>
@@ -11160,10 +11160,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B346" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C346" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D346" s="0" t="s">
         <x:v>236</x:v>
@@ -11189,10 +11189,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B347" s="0">
-        <x:v>13.22</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C347" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D347" s="0" t="s">
         <x:v>236</x:v>
@@ -11218,10 +11218,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B348" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C348" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D348" s="0" t="s">
         <x:v>236</x:v>
@@ -11247,10 +11247,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B349" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C349" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D349" s="0" t="s">
         <x:v>236</x:v>
@@ -11276,10 +11276,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B350" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C350" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D350" s="0" t="s">
         <x:v>236</x:v>
@@ -11305,10 +11305,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B351" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C351" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D351" s="0" t="s">
         <x:v>237</x:v>
@@ -11334,10 +11334,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B352" s="0">
-        <x:v>13.22</x:v>
+        <x:v>12.9</x:v>
       </x:c>
       <x:c r="C352" s="0">
-        <x:v>-0.72</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D352" s="0" t="s">
         <x:v>238</x:v>
@@ -11363,10 +11363,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B353" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C353" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D353" s="0" t="s">
         <x:v>238</x:v>
@@ -11392,10 +11392,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B354" s="0">
-        <x:v>18.86</x:v>
+        <x:v>17.95</x:v>
       </x:c>
       <x:c r="C354" s="0">
-        <x:v>-0.25</x:v>
+        <x:v>-0.91</x:v>
       </x:c>
       <x:c r="D354" s="0" t="s">
         <x:v>239</x:v>
@@ -11421,10 +11421,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B355" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C355" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D355" s="0" t="s">
         <x:v>239</x:v>
@@ -11450,10 +11450,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B356" s="0">
-        <x:v>16.2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C356" s="0">
-        <x:v>-0.92</x:v>
+        <x:v>-0.2</x:v>
       </x:c>
       <x:c r="D356" s="0" t="s">
         <x:v>239</x:v>
@@ -11479,10 +11479,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B357" s="0">
-        <x:v>340.25</x:v>
+        <x:v>322.25</x:v>
       </x:c>
       <x:c r="C357" s="0">
-        <x:v>-10.75</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="D357" s="0" t="s">
         <x:v>240</x:v>
@@ -11508,10 +11508,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B358" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C358" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D358" s="0" t="s">
         <x:v>240</x:v>
@@ -11537,10 +11537,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B359" s="0">
-        <x:v>7.97</x:v>
+        <x:v>7.65</x:v>
       </x:c>
       <x:c r="C359" s="0">
-        <x:v>-0.26</x:v>
+        <x:v>-0.32</x:v>
       </x:c>
       <x:c r="D359" s="0" t="s">
         <x:v>240</x:v>
@@ -11566,10 +11566,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B360" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C360" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D360" s="0" t="s">
         <x:v>240</x:v>
@@ -11595,10 +11595,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B361" s="0">
-        <x:v>17.67</x:v>
+        <x:v>19.43</x:v>
       </x:c>
       <x:c r="C361" s="0">
-        <x:v>-0.75</x:v>
+        <x:v>1.76</x:v>
       </x:c>
       <x:c r="D361" s="0" t="s">
         <x:v>240</x:v>
@@ -11624,10 +11624,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B362" s="0">
-        <x:v>8.75</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="C362" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D362" s="0" t="s">
         <x:v>241</x:v>
@@ -11653,10 +11653,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B363" s="0">
-        <x:v>8.75</x:v>
+        <x:v>8.21</x:v>
       </x:c>
       <x:c r="C363" s="0">
-        <x:v>-0.11</x:v>
+        <x:v>-0.54</x:v>
       </x:c>
       <x:c r="D363" s="0" t="s">
         <x:v>241</x:v>
@@ -11682,10 +11682,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B364" s="0">
-        <x:v>12.28</x:v>
+        <x:v>11.06</x:v>
       </x:c>
       <x:c r="C364" s="0">
-        <x:v>-1.36</x:v>
+        <x:v>-1.22</x:v>
       </x:c>
       <x:c r="D364" s="0" t="s">
         <x:v>241</x:v>
@@ -11711,10 +11711,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B365" s="0">
-        <x:v>3.19</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="C365" s="0">
-        <x:v>-0.15</x:v>
+        <x:v>-0.09</x:v>
       </x:c>
       <x:c r="D365" s="0" t="s">
         <x:v>241</x:v>
@@ -11740,10 +11740,10 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B366" s="0">
-        <x:v>12.16</x:v>
+        <x:v>11.75</x:v>
       </x:c>
       <x:c r="C366" s="0">
-        <x:v>0.25</x:v>
+        <x:v>-0.41</x:v>
       </x:c>
       <x:c r="D366" s="0" t="s">
         <x:v>241</x:v>
@@ -11769,10 +11769,10 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="B367" s="0">
-        <x:v>9.64</x:v>
+        <x:v>9.16</x:v>
       </x:c>
       <x:c r="C367" s="0">
-        <x:v>-0.08</x:v>
+        <x:v>-0.48</x:v>
       </x:c>
       <x:c r="D367" s="0" t="s">
         <x:v>245</x:v>
@@ -11798,10 +11798,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B368" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C368" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D368" s="0" t="s">
         <x:v>245</x:v>
@@ -11827,10 +11827,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B369" s="0">
-        <x:v>3.19</x:v>
+        <x:v>2.98</x:v>
       </x:c>
       <x:c r="C369" s="0">
-        <x:v>-0.16</x:v>
+        <x:v>-0.21</x:v>
       </x:c>
       <x:c r="D369" s="0" t="s">
         <x:v>245</x:v>
@@ -11856,10 +11856,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B370" s="0">
-        <x:v>9.39</x:v>
+        <x:v>8.67</x:v>
       </x:c>
       <x:c r="C370" s="0">
-        <x:v>-1.04</x:v>
+        <x:v>-0.72</x:v>
       </x:c>
       <x:c r="D370" s="0" t="s">
         <x:v>246</x:v>
@@ -11885,10 +11885,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B371" s="0">
-        <x:v>26.14</x:v>
+        <x:v>25.1</x:v>
       </x:c>
       <x:c r="C371" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-1.04</x:v>
       </x:c>
       <x:c r="D371" s="0" t="s">
         <x:v>246</x:v>
@@ -11914,10 +11914,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B372" s="0">
-        <x:v>444.5</x:v>
+        <x:v>400.25</x:v>
       </x:c>
       <x:c r="C372" s="0">
-        <x:v>-49.25</x:v>
+        <x:v>-44.25</x:v>
       </x:c>
       <x:c r="D372" s="0" t="s">
         <x:v>246</x:v>
@@ -11943,10 +11943,10 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="B373" s="0">
-        <x:v>3.89</x:v>
+        <x:v>3.56</x:v>
       </x:c>
       <x:c r="C373" s="0">
-        <x:v>-0.1</x:v>
+        <x:v>-0.33</x:v>
       </x:c>
       <x:c r="D373" s="0" t="s">
         <x:v>248</x:v>
@@ -11972,10 +11972,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B374" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C374" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D374" s="0" t="s">
         <x:v>248</x:v>
@@ -12001,10 +12001,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B375" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C375" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D375" s="0" t="s">
         <x:v>248</x:v>
@@ -12030,10 +12030,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B376" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C376" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D376" s="0" t="s">
         <x:v>248</x:v>
@@ -12059,10 +12059,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B377" s="0">
-        <x:v>12.28</x:v>
+        <x:v>11.06</x:v>
       </x:c>
       <x:c r="C377" s="0">
-        <x:v>-1.36</x:v>
+        <x:v>-1.22</x:v>
       </x:c>
       <x:c r="D377" s="0" t="s">
         <x:v>248</x:v>
@@ -12088,10 +12088,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B378" s="0">
-        <x:v>35.36</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="C378" s="0">
-        <x:v>-1.44</x:v>
+        <x:v>-2.28</x:v>
       </x:c>
       <x:c r="D378" s="0" t="s">
         <x:v>248</x:v>
@@ -12117,10 +12117,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B379" s="0">
-        <x:v>21.04</x:v>
+        <x:v>19.6</x:v>
       </x:c>
       <x:c r="C379" s="0">
-        <x:v>-0.96</x:v>
+        <x:v>-1.44</x:v>
       </x:c>
       <x:c r="D379" s="0" t="s">
         <x:v>250</x:v>
@@ -12146,10 +12146,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B380" s="0">
-        <x:v>12.28</x:v>
+        <x:v>11.06</x:v>
       </x:c>
       <x:c r="C380" s="0">
-        <x:v>-1.36</x:v>
+        <x:v>-1.22</x:v>
       </x:c>
       <x:c r="D380" s="0" t="s">
         <x:v>251</x:v>
@@ -12175,10 +12175,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B381" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.66</x:v>
       </x:c>
       <x:c r="C381" s="0">
-        <x:v>-0.62</x:v>
+        <x:v>-0.76</x:v>
       </x:c>
       <x:c r="D381" s="0" t="s">
         <x:v>252</x:v>
@@ -12204,10 +12204,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B382" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C382" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D382" s="0" t="s">
         <x:v>252</x:v>
@@ -12233,10 +12233,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B383" s="0">
-        <x:v>11.97</x:v>
+        <x:v>11.42</x:v>
       </x:c>
       <x:c r="C383" s="0">
-        <x:v>-0.52</x:v>
+        <x:v>-0.55</x:v>
       </x:c>
       <x:c r="D383" s="0" t="s">
         <x:v>253</x:v>
@@ -12262,10 +12262,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B384" s="0">
-        <x:v>21.4</x:v>
+        <x:v>20.78</x:v>
       </x:c>
       <x:c r="C384" s="0">
-        <x:v>-0.98</x:v>
+        <x:v>-0.62</x:v>
       </x:c>
       <x:c r="D384" s="0" t="s">
         <x:v>254</x:v>
@@ -12291,10 +12291,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B385" s="0">
-        <x:v>2.51</x:v>
+        <x:v>2.52</x:v>
       </x:c>
       <x:c r="C385" s="0">
-        <x:v>-0.19</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="D385" s="0" t="s">
         <x:v>256</x:v>
@@ -12320,10 +12320,10 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B386" s="0">
-        <x:v>61.2</x:v>
+        <x:v>59.5</x:v>
       </x:c>
       <x:c r="C386" s="0">
-        <x:v>-3.2</x:v>
+        <x:v>-1.7</x:v>
       </x:c>
       <x:c r="D386" s="0" t="s">
         <x:v>257</x:v>
@@ -12349,10 +12349,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B387" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C387" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D387" s="0" t="s">
         <x:v>257</x:v>
@@ -12378,10 +12378,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B388" s="0">
-        <x:v>0.54</x:v>
+        <x:v>0.51</x:v>
       </x:c>
       <x:c r="C388" s="0">
-        <x:v>-0.06</x:v>
+        <x:v>-0.03</x:v>
       </x:c>
       <x:c r="D388" s="0" t="s">
         <x:v>258</x:v>
@@ -12407,10 +12407,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B389" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C389" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D389" s="0" t="s">
         <x:v>259</x:v>
@@ -12436,10 +12436,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B390" s="0">
-        <x:v>89.1</x:v>
+        <x:v>83.3</x:v>
       </x:c>
       <x:c r="C390" s="0">
-        <x:v>-2.55</x:v>
+        <x:v>-5.8</x:v>
       </x:c>
       <x:c r="D390" s="0" t="s">
         <x:v>259</x:v>
@@ -12465,10 +12465,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B391" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C391" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D391" s="0" t="s">
         <x:v>259</x:v>
@@ -12494,10 +12494,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B392" s="0">
-        <x:v>4.3</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="C392" s="0">
-        <x:v>-0.28</x:v>
+        <x:v>-0.26</x:v>
       </x:c>
       <x:c r="D392" s="0" t="s">
         <x:v>259</x:v>
@@ -12523,10 +12523,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B393" s="0">
-        <x:v>164.9</x:v>
+        <x:v>160.6</x:v>
       </x:c>
       <x:c r="C393" s="0">
-        <x:v>-18.3</x:v>
+        <x:v>-4.3</x:v>
       </x:c>
       <x:c r="D393" s="0" t="s">
         <x:v>260</x:v>
@@ -12552,10 +12552,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B394" s="0">
-        <x:v>60.45</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="C394" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="D394" s="0" t="s">
         <x:v>260</x:v>
@@ -12581,10 +12581,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B395" s="0">
-        <x:v>77.1</x:v>
+        <x:v>80.05</x:v>
       </x:c>
       <x:c r="C395" s="0">
-        <x:v>7</x:v>
+        <x:v>2.95</x:v>
       </x:c>
       <x:c r="D395" s="0" t="s">
         <x:v>260</x:v>
